--- a/model/Outputs/11. Interest rate/30/Output Files/0.1/Output_39_36.xlsx
+++ b/model/Outputs/11. Interest rate/30/Output Files/0.1/Output_39_36.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2473914.835921463</v>
+        <v>2474280.688654416</v>
       </c>
     </row>
     <row r="7">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15007297.66423092</v>
+        <v>14202765.50069438</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15811829.82776745</v>
+        <v>15811829.82776744</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>43034912.63292718</v>
+        <v>44575262.7454409</v>
       </c>
     </row>
   </sheetData>
@@ -654,22 +654,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81.99931295557451</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>49.47457824299391</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>10.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>4.363289606868648</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>4.889628708011855</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>2.121191382493578</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -702,25 +702,25 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>86.63387031607222</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>57.56369544051387</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>85.9740142491881</v>
       </c>
       <c r="U2" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
         <v>229.8510241668239</v>
       </c>
       <c r="W2" t="n">
-        <v>38.43482075799123</v>
+        <v>235</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>192.2818334606677</v>
       </c>
       <c r="Y2" t="n">
         <v>111.3174326828064</v>
@@ -778,13 +778,13 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>61.330887731989</v>
       </c>
       <c r="R3" t="n">
         <v>92.92009917917176</v>
       </c>
       <c r="S3" t="n">
-        <v>79.86560590103308</v>
+        <v>219.1613115321363</v>
       </c>
       <c r="T3" t="n">
         <v>1.829152009966663</v>
@@ -793,16 +793,16 @@
         <v>235</v>
       </c>
       <c r="V3" t="n">
-        <v>235</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W3" t="n">
         <v>32.37314290982852</v>
       </c>
       <c r="X3" t="n">
+        <v>19.86273944538755</v>
+      </c>
+      <c r="Y3" t="n">
         <v>235</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -848,10 +848,10 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>16.28947281805793</v>
       </c>
       <c r="O4" t="n">
-        <v>16.28947281805793</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -894,10 +894,10 @@
         <v>81.99931295557451</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>49.47457824299391</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>10.33915573984979</v>
       </c>
       <c r="E5" t="n">
         <v>4.363289606868648</v>
@@ -942,25 +942,25 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>57.56369544051385</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>179.5131998190161</v>
       </c>
       <c r="U5" t="n">
-        <v>168.4925398100652</v>
+        <v>225.135502051709</v>
       </c>
       <c r="V5" t="n">
-        <v>229.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>192.2818334606677</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>111.3174326828064</v>
       </c>
     </row>
     <row r="6">
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>235</v>
+        <v>91.43931248226409</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1015,13 +1015,13 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>61.330887731989</v>
       </c>
       <c r="R6" t="n">
         <v>235</v>
       </c>
       <c r="S6" t="n">
-        <v>138.2595330227329</v>
+        <v>235</v>
       </c>
       <c r="T6" t="n">
         <v>1.829152009966647</v>
@@ -1030,7 +1030,7 @@
         <v>0.1527654205641062</v>
       </c>
       <c r="V6" t="n">
-        <v>14.51066719152016</v>
+        <v>235</v>
       </c>
       <c r="W6" t="n">
         <v>32.37314290982852</v>
@@ -1085,16 +1085,16 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>16.28947281805793</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>81.99931295557451</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
         <v>49.47457824299391</v>
@@ -1143,7 +1143,7 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2.121191382493598</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1182,7 +1182,7 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>67.20089017630799</v>
       </c>
       <c r="U8" t="n">
         <v>235</v>
@@ -1197,7 +1197,7 @@
         <v>192.2818334606677</v>
       </c>
       <c r="Y8" t="n">
-        <v>98.64020128603346</v>
+        <v>111.3174326828064</v>
       </c>
     </row>
     <row r="9">
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>186.9853481554995</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>61.330887731989</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>235</v>
@@ -1267,13 +1267,13 @@
         <v>0.1527654205641062</v>
       </c>
       <c r="V9" t="n">
-        <v>14.51066719152016</v>
+        <v>200.7848520587536</v>
       </c>
       <c r="W9" t="n">
         <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>96.79138473613149</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1295,46 +1295,46 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
         <v>16.28947281805793</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1368,7 +1368,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -1380,13 +1380,13 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>213.9092564389587</v>
       </c>
       <c r="H11" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>142.6493110848568</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1401,7 +1401,7 @@
         <v>191.963077391061</v>
       </c>
       <c r="N11" t="n">
-        <v>139.8587137640661</v>
+        <v>120.3011088236041</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1416,13 +1416,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>210.3493111062823</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>27.05165151992229</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -1453,7 +1453,7 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1.613364378340986</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>31.66503142941086</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1513,7 +1513,7 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>204.9483329489301</v>
       </c>
     </row>
     <row r="13">
@@ -1602,13 +1602,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>33.86680861750629</v>
       </c>
       <c r="D14" t="n">
-        <v>181.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1620,7 +1620,7 @@
         <v>173.1211913824936</v>
       </c>
       <c r="H14" t="n">
-        <v>162.2531210150852</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1635,10 +1635,10 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>27.96307739106101</v>
+        <v>59.53475375990635</v>
       </c>
       <c r="N14" t="n">
-        <v>31.57167636884533</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1653,10 +1653,10 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>228.5636954405139</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>166.7108364220575</v>
+        <v>235</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1684,10 +1684,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>132.0999124455193</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>118.9376868977026</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1696,10 +1696,10 @@
         <v>110.6362423378769</v>
       </c>
       <c r="G15" t="n">
-        <v>95.86410191276319</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>94.71323812981736</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1729,10 +1729,10 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>112.1744909373787</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>221.3031980778188</v>
       </c>
       <c r="T15" t="n">
         <v>172.8291520099666</v>
@@ -1741,16 +1741,16 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>32.68381610431634</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>190.8627394453875</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>170.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1775,7 +1775,7 @@
         <v>45.38285596774193</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>15.30993841530052</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1793,13 +1793,13 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>176.5840540255007</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>221.2782054420873</v>
+        <v>229.8730916651275</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>152.67922938716</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1845,19 +1845,19 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>180.3391557398498</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>174.3632896068686</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>168.4687381976824</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>161.2531210150852</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1872,10 +1872,10 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>26.96307739106101</v>
+        <v>59.53475375990635</v>
       </c>
       <c r="N17" t="n">
-        <v>32.57167636884537</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -1893,13 +1893,13 @@
         <v>227.5636954405139</v>
       </c>
       <c r="T17" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>214.4243045594861</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
@@ -1924,19 +1924,19 @@
         <v>131.0999124455193</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>117.9376868977026</v>
       </c>
       <c r="E18" t="n">
-        <v>112.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>109.6362423378769</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>93.71323812981736</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1969,25 +1969,25 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>220.3031980778188</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>171.8291520099666</v>
       </c>
       <c r="U18" t="n">
-        <v>170.1527654205641</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>184.5106671915202</v>
+        <v>50.4107693925502</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>135.1010733106172</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>169.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>43.3822030078342</v>
       </c>
       <c r="C19" t="n">
         <v>42.72524664804467</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>55.53621805555548</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>50.98090483695654</v>
       </c>
       <c r="F19" t="n">
         <v>44.38285596774193</v>
@@ -2027,13 +2027,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>84.43159537089392</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>228.8730916651275</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2045,7 +2045,7 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -2066,7 +2066,7 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>57.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2079,13 +2079,13 @@
         <v>235</v>
       </c>
       <c r="C20" t="n">
-        <v>219.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>180.3391557398498</v>
+        <v>166.4819606700342</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>174.3632896068686</v>
       </c>
       <c r="F20" t="n">
         <v>174.8896287080119</v>
@@ -2094,7 +2094,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>161.2531210150852</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2109,10 +2109,10 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>26.96307739106101</v>
+        <v>59.53475375990635</v>
       </c>
       <c r="N20" t="n">
-        <v>32.57167636884537</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2145,7 +2145,7 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>102.2846373091443</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2161,19 +2161,19 @@
         <v>131.0999124455193</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>117.9376868977026</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>112.6720972219126</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>109.6362423378769</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>94.86410191276319</v>
       </c>
       <c r="H21" t="n">
-        <v>93.71323812981734</v>
+        <v>93.71323812981736</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2209,19 +2209,19 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>141.8427292707975</v>
+        <v>76.8041721303109</v>
       </c>
       <c r="U21" t="n">
         <v>170.1527654205641</v>
       </c>
       <c r="V21" t="n">
-        <v>184.5106671915202</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>189.8627394453875</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -2243,13 +2243,13 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>50.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>14.30993841530054</v>
+        <v>14.30993841530052</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -2279,10 +2279,10 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>23.42197468903189</v>
+        <v>235</v>
       </c>
       <c r="R22" t="n">
-        <v>235</v>
+        <v>82.00278874526677</v>
       </c>
       <c r="S22" t="n">
         <v>119.5830042930194</v>
@@ -2313,25 +2313,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>182.0073824270403</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>219.4745782429939</v>
       </c>
       <c r="D23" t="n">
-        <v>180.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>174.3632896068686</v>
       </c>
       <c r="F23" t="n">
         <v>174.8896287080119</v>
       </c>
       <c r="G23" t="n">
-        <v>86.75921555213826</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>161.2531210150852</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2346,10 +2346,10 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>59.53475375990635</v>
       </c>
       <c r="N23" t="n">
-        <v>59.53475375990635</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2376,13 +2376,13 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>154.5565566463266</v>
       </c>
       <c r="C24" t="n">
-        <v>131.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>117.9376868977026</v>
@@ -2410,7 +2410,7 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>93.71323812981734</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2440,19 +2440,19 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="S24" t="n">
-        <v>43.91787657735971</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>171.8291520099667</v>
+        <v>171.8291520099666</v>
       </c>
       <c r="U24" t="n">
-        <v>170.1527654205641</v>
+        <v>31.0961365457357</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>184.5106671915202</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>169.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2471,22 +2471,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>57.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>55.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>44.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>14.30993841530054</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
         <v>175.5840540255007</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>61.42337449063198</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -2519,10 +2519,10 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="S25" t="n">
-        <v>119.5830042930194</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2556,16 +2556,16 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>96.02028891514139</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>137.0000000000003</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>137.0000000000005</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>137.000000000001</v>
       </c>
       <c r="H26" t="n">
         <v>137.000000000001</v>
@@ -2583,10 +2583,10 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>108.6732645447071</v>
+        <v>73.96307739106101</v>
       </c>
       <c r="N26" t="n">
-        <v>2.301108823604068</v>
+        <v>37.01129597725013</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -2604,10 +2604,10 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>137.0000000000009</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>96.02028891514043</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2632,13 +2632,13 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>137.0000000000005</v>
+        <v>137.0000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>137.0000000000006</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>118.930661749417</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -2686,7 +2686,7 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>137.0000000000011</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -2698,7 +2698,7 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>137.0000000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2726,7 +2726,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>18.09990058392311</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -2756,7 +2756,7 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>45.72052306281815</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2768,10 +2768,10 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>16.17031021621619</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>43.37280983870968</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -2790,19 +2790,19 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>137.0000000000008</v>
+        <v>137.0000000000005</v>
       </c>
       <c r="D29" t="n">
-        <v>137.0000000000008</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>137.0000000000007</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>120.6695999999976</v>
+        <v>137.0000000000013</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -2823,7 +2823,7 @@
         <v>55.96307739106101</v>
       </c>
       <c r="N29" t="n">
-        <v>55.01129597725058</v>
+        <v>55.01129597725036</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -2844,7 +2844,7 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>137.0000000000013</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -2853,7 +2853,7 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>120.6695999999969</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -2866,7 +2866,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>137.0000000000006</v>
+        <v>8.571519679393136</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -2878,10 +2878,10 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>137.0000000000007</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>123.8641019127632</v>
       </c>
       <c r="H30" t="n">
         <v>122.7132381298174</v>
@@ -2923,10 +2923,10 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>137.0000000000011</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>137.0000000000005</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
@@ -2935,7 +2935,7 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>132.435621592157</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2951,7 +2951,7 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>25.55599175010089</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -2975,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>56.81746645572439</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -2993,13 +2993,13 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
         <v>137</v>
       </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>5.888664866913452</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>25.37280983870968</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
@@ -3030,7 +3030,7 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>137.0000000000006</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -3075,19 +3075,19 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
+        <v>120.6695999999974</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
         <v>137.0000000000011</v>
       </c>
-      <c r="T32" t="n">
-        <v>120.6695999999973</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
       <c r="V32" t="n">
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>137.0000000000004</v>
       </c>
       <c r="X32" t="n">
         <v>0</v>
@@ -3112,13 +3112,13 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>137.0000000000006</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>137.0000000000005</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>118.1488597219727</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -3151,25 +3151,25 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>137.0000000000014</v>
+        <v>118.1488597219736</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>137.0000000000009</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>137.0000000000004</v>
       </c>
       <c r="W33" t="n">
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>137.0000000000004</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -3182,10 +3182,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>86.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>71.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -3197,10 +3197,10 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>10.78055587981815</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>21.24578183932354</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -3227,16 +3227,16 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>25.55599175010201</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>5.888664866913444</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -3245,10 +3245,10 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>25.37280983870968</v>
       </c>
       <c r="X34" t="n">
-        <v>46.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
         <v>0</v>
@@ -3267,19 +3267,19 @@
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>137.0000000000006</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>137.0000000000005</v>
+        <v>137.0000000000007</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>137.0000000000009</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>120.669599999998</v>
+        <v>137.0000000000012</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3294,10 +3294,10 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>110.9743733683114</v>
+        <v>55.96307739106101</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>55.01129597725036</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -3312,10 +3312,10 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>137.0000000000014</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>120.6695999999967</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -3340,25 +3340,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>137.0000000000004</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>137.0000000000007</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>137.0000000000009</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>132.4356215921562</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>122.7132381298173</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -3394,10 +3394,10 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>137.0000000000009</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>137.000000000001</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -3409,7 +3409,7 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>118.1488597219737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>81.97930376755419</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
@@ -3449,10 +3449,10 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>113.4315953708939</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>49.12439637920854</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>5.888664866913444</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -3488,7 +3488,7 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>86.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -3501,13 +3501,13 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>120.6695999999962</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>137.0000000000007</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -3516,7 +3516,7 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>137.0000000000014</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3531,10 +3531,10 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>110.9743733683114</v>
+        <v>55.96307739106101</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>55.01129597725036</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -3549,16 +3549,16 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>137.0000000000016</v>
+        <v>137.0000000000013</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>137.0000000000011</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>137.0000000000013</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>120.6695999999964</v>
       </c>
       <c r="W38" t="n">
         <v>0</v>
@@ -3595,7 +3595,7 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>118.1488597219724</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3631,22 +3631,22 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>137.0000000000011</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>137.0000000000013</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>137.0000000000006</v>
+        <v>137.0000000000005</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>137.0000000000005</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>118.1488597219736</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>137.0000000000005</v>
       </c>
     </row>
     <row r="40">
@@ -3674,7 +3674,7 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>21.24578183932353</v>
+        <v>21.24578183932354</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -3686,7 +3686,7 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>4.365392252595433</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -3707,10 +3707,10 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>90.83074510205691</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>5.888664866913452</v>
+        <v>5.888664866913444</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -3725,7 +3725,7 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>86.46535284946236</v>
       </c>
     </row>
     <row r="41">
@@ -3750,13 +3750,13 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>137.0000000000013</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>137.0000000000013</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>24.64931108485681</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3768,10 +3768,10 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>73.96307739106101</v>
+        <v>108.6732645447073</v>
       </c>
       <c r="N41" t="n">
-        <v>37.01129597725035</v>
+        <v>2.301108823604068</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -3792,16 +3792,16 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>96.02028891513982</v>
+        <v>137.0000000000012</v>
       </c>
       <c r="V41" t="n">
-        <v>137.0000000000007</v>
+        <v>120.6695999999977</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>137.0000000000005</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>137.0000000000006</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
@@ -3814,10 +3814,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>137.0000000000008</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>137.0000000000007</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -3826,16 +3826,16 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>137.0000000000006</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>137.0000000000011</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>21.71293004802855</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3862,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>21.44163906895242</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -3871,10 +3871,10 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>129.1758884950336</v>
       </c>
       <c r="V42" t="n">
-        <v>137.0000000000006</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>70.08846865943244</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -3947,16 +3947,16 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>23.88866486691345</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>16.17031021621619</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>43.37280983870968</v>
       </c>
       <c r="X43" t="n">
         <v>0</v>
@@ -3972,10 +3972,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>137.0000000000003</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>137.0000000000003</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>137.0000000000005</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -4005,11 +4005,11 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
         <v>137.0000000000013</v>
       </c>
-      <c r="N44" t="n">
-        <v>137.0000000000015</v>
-      </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
@@ -4020,13 +4020,13 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>137.000000000001</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>137.0000000000008</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>94.64397336830882</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -4038,7 +4038,7 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>94.64397336830689</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -4066,13 +4066,13 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>137.0000000000007</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>81.06654000898236</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>18.54682436935798</v>
@@ -4087,7 +4087,7 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>122.0961940438275</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -4099,7 +4099,7 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>95.97034596515547</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -4297,19 +4297,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>90.7069128083008</v>
+        <v>18.8</v>
       </c>
       <c r="C2" t="n">
-        <v>40.73259135073118</v>
+        <v>18.8</v>
       </c>
       <c r="D2" t="n">
-        <v>30.28899969431725</v>
+        <v>18.8</v>
       </c>
       <c r="E2" t="n">
-        <v>25.88163645505599</v>
+        <v>18.8</v>
       </c>
       <c r="F2" t="n">
-        <v>20.94261755807432</v>
+        <v>18.8</v>
       </c>
       <c r="G2" t="n">
         <v>18.8</v>
@@ -4345,28 +4345,28 @@
         <v>940</v>
       </c>
       <c r="R2" t="n">
-        <v>852.4910400847755</v>
+        <v>940</v>
       </c>
       <c r="S2" t="n">
-        <v>794.3458931751655</v>
+        <v>881.8548530903901</v>
       </c>
       <c r="T2" t="n">
-        <v>794.3458931751655</v>
+        <v>795.0124144548465</v>
       </c>
       <c r="U2" t="n">
-        <v>556.9721558014281</v>
+        <v>795.0124144548465</v>
       </c>
       <c r="V2" t="n">
-        <v>324.7994041177676</v>
+        <v>562.839662771186</v>
       </c>
       <c r="W2" t="n">
-        <v>285.9763528470694</v>
+        <v>325.4659253974486</v>
       </c>
       <c r="X2" t="n">
-        <v>285.9763528470694</v>
+        <v>131.2418511947539</v>
       </c>
       <c r="Y2" t="n">
-        <v>173.5345016523154</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="3">
@@ -4400,49 +4400,49 @@
         <v>18.8</v>
       </c>
       <c r="J3" t="n">
-        <v>224.6387383828462</v>
+        <v>18.8</v>
       </c>
       <c r="K3" t="n">
-        <v>338.3103324130147</v>
+        <v>55.02113056452833</v>
       </c>
       <c r="L3" t="n">
-        <v>413.63206459226</v>
+        <v>175.6573997895532</v>
       </c>
       <c r="M3" t="n">
-        <v>646.28206459226</v>
+        <v>408.3073997895532</v>
       </c>
       <c r="N3" t="n">
-        <v>646.28206459226</v>
+        <v>640.9573997895532</v>
       </c>
       <c r="O3" t="n">
-        <v>878.93206459226</v>
+        <v>707.35</v>
       </c>
       <c r="P3" t="n">
         <v>940</v>
       </c>
       <c r="Q3" t="n">
-        <v>940</v>
+        <v>878.0496083515262</v>
       </c>
       <c r="R3" t="n">
-        <v>846.1413139604326</v>
+        <v>784.1909223119587</v>
       </c>
       <c r="S3" t="n">
-        <v>765.4689847674699</v>
+        <v>562.8158601582857</v>
       </c>
       <c r="T3" t="n">
-        <v>763.6213564745743</v>
+        <v>560.9682318653901</v>
       </c>
       <c r="U3" t="n">
-        <v>526.2476191008369</v>
+        <v>323.5944944916527</v>
       </c>
       <c r="V3" t="n">
-        <v>288.8738817270995</v>
+        <v>308.9372549042586</v>
       </c>
       <c r="W3" t="n">
+        <v>276.2371105508965</v>
+      </c>
+      <c r="X3" t="n">
         <v>256.1737373737374</v>
-      </c>
-      <c r="X3" t="n">
-        <v>18.8</v>
       </c>
       <c r="Y3" t="n">
         <v>18.8</v>
@@ -4491,7 +4491,7 @@
         <v>35.25401294753327</v>
       </c>
       <c r="N4" t="n">
-        <v>35.25401294753327</v>
+        <v>18.8</v>
       </c>
       <c r="O4" t="n">
         <v>18.8</v>
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.20736323926126</v>
+        <v>83.6252763532448</v>
       </c>
       <c r="C5" t="n">
-        <v>23.20736323926126</v>
+        <v>33.65095489567519</v>
       </c>
       <c r="D5" t="n">
         <v>23.20736323926126</v>
@@ -4585,25 +4585,25 @@
         <v>940</v>
       </c>
       <c r="S5" t="n">
-        <v>940</v>
+        <v>881.8548530903901</v>
       </c>
       <c r="T5" t="n">
-        <v>940</v>
+        <v>700.5283886267374</v>
       </c>
       <c r="U5" t="n">
-        <v>769.8055153433685</v>
+        <v>473.1187905947081</v>
       </c>
       <c r="V5" t="n">
-        <v>537.632763659708</v>
+        <v>473.1187905947081</v>
       </c>
       <c r="W5" t="n">
-        <v>300.2590262859706</v>
+        <v>473.1187905947081</v>
       </c>
       <c r="X5" t="n">
-        <v>106.0349520832759</v>
+        <v>278.8947163920134</v>
       </c>
       <c r="Y5" t="n">
-        <v>106.0349520832759</v>
+        <v>166.4528651972595</v>
       </c>
     </row>
     <row r="6">
@@ -4613,13 +4613,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>493.5474747474748</v>
+        <v>111.1629419012769</v>
       </c>
       <c r="C6" t="n">
-        <v>493.5474747474748</v>
+        <v>111.1629419012769</v>
       </c>
       <c r="D6" t="n">
-        <v>256.1737373737374</v>
+        <v>111.1629419012769</v>
       </c>
       <c r="E6" t="n">
         <v>18.8</v>
@@ -4646,43 +4646,43 @@
         <v>336.1816011266198</v>
       </c>
       <c r="M6" t="n">
-        <v>568.8316011266198</v>
+        <v>474.7</v>
       </c>
       <c r="N6" t="n">
-        <v>801.4816011266198</v>
+        <v>474.7</v>
       </c>
       <c r="O6" t="n">
-        <v>878.93206459226</v>
+        <v>707.35</v>
       </c>
       <c r="P6" t="n">
         <v>940</v>
       </c>
       <c r="Q6" t="n">
-        <v>940</v>
+        <v>878.0496083515262</v>
       </c>
       <c r="R6" t="n">
-        <v>702.6262626262626</v>
+        <v>640.6758709777888</v>
       </c>
       <c r="S6" t="n">
-        <v>562.9701686639061</v>
+        <v>403.3021336040514</v>
       </c>
       <c r="T6" t="n">
-        <v>561.1225403710105</v>
+        <v>401.4545053111558</v>
       </c>
       <c r="U6" t="n">
-        <v>560.9682318653902</v>
+        <v>401.3001968055355</v>
       </c>
       <c r="V6" t="n">
-        <v>546.3109922779961</v>
+        <v>163.9264594317981</v>
       </c>
       <c r="W6" t="n">
-        <v>513.610847924634</v>
+        <v>131.226315078436</v>
       </c>
       <c r="X6" t="n">
-        <v>493.5474747474748</v>
+        <v>111.1629419012769</v>
       </c>
       <c r="Y6" t="n">
-        <v>493.5474747474748</v>
+        <v>111.1629419012769</v>
       </c>
     </row>
     <row r="7">
@@ -4728,13 +4728,13 @@
         <v>35.25401294753327</v>
       </c>
       <c r="N7" t="n">
-        <v>18.8</v>
+        <v>35.25401294753327</v>
       </c>
       <c r="O7" t="n">
-        <v>18.8</v>
+        <v>35.25401294753327</v>
       </c>
       <c r="P7" t="n">
-        <v>18.8</v>
+        <v>35.25401294753327</v>
       </c>
       <c r="Q7" t="n">
         <v>18.8</v>
@@ -4771,19 +4771,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>88.56429525022648</v>
+        <v>90.70691280830081</v>
       </c>
       <c r="C8" t="n">
-        <v>38.58997379265686</v>
+        <v>40.73259135073121</v>
       </c>
       <c r="D8" t="n">
-        <v>28.14638213624293</v>
+        <v>30.28899969431728</v>
       </c>
       <c r="E8" t="n">
-        <v>23.73901889698167</v>
+        <v>25.88163645505601</v>
       </c>
       <c r="F8" t="n">
-        <v>18.8</v>
+        <v>20.94261755807434</v>
       </c>
       <c r="G8" t="n">
         <v>18.8</v>
@@ -4825,22 +4825,22 @@
         <v>940</v>
       </c>
       <c r="T8" t="n">
-        <v>940</v>
+        <v>872.1203129532242</v>
       </c>
       <c r="U8" t="n">
-        <v>702.6262626262626</v>
+        <v>634.7465755794868</v>
       </c>
       <c r="V8" t="n">
-        <v>702.6262626262626</v>
+        <v>634.7465755794868</v>
       </c>
       <c r="W8" t="n">
-        <v>465.2525252525252</v>
+        <v>397.3728382057494</v>
       </c>
       <c r="X8" t="n">
-        <v>271.0284510498305</v>
+        <v>203.1487640030547</v>
       </c>
       <c r="Y8" t="n">
-        <v>171.3918840942411</v>
+        <v>90.70691280830081</v>
       </c>
     </row>
     <row r="9">
@@ -4850,25 +4850,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>256.1737373737374</v>
+        <v>207.6740890459591</v>
       </c>
       <c r="C9" t="n">
-        <v>256.1737373737374</v>
+        <v>207.6740890459591</v>
       </c>
       <c r="D9" t="n">
-        <v>256.1737373737374</v>
+        <v>207.6740890459591</v>
       </c>
       <c r="E9" t="n">
-        <v>256.1737373737374</v>
+        <v>207.6740890459591</v>
       </c>
       <c r="F9" t="n">
-        <v>18.8</v>
+        <v>207.6740890459591</v>
       </c>
       <c r="G9" t="n">
-        <v>18.8</v>
+        <v>207.6740890459591</v>
       </c>
       <c r="H9" t="n">
-        <v>18.8</v>
+        <v>207.6740890459591</v>
       </c>
       <c r="I9" t="n">
         <v>18.8</v>
@@ -4877,49 +4877,49 @@
         <v>224.6387383828462</v>
       </c>
       <c r="K9" t="n">
-        <v>457.2887383828462</v>
+        <v>260.8598689473745</v>
       </c>
       <c r="L9" t="n">
-        <v>532.6104705620915</v>
+        <v>336.1816011266198</v>
       </c>
       <c r="M9" t="n">
-        <v>765.2604705620914</v>
+        <v>336.1816011266198</v>
       </c>
       <c r="N9" t="n">
-        <v>765.2604705620914</v>
+        <v>474.7</v>
       </c>
       <c r="O9" t="n">
-        <v>831.6530707725383</v>
+        <v>707.35</v>
       </c>
       <c r="P9" t="n">
         <v>940</v>
       </c>
       <c r="Q9" t="n">
-        <v>878.0496083515262</v>
+        <v>940</v>
       </c>
       <c r="R9" t="n">
-        <v>640.6758709777888</v>
+        <v>702.6262626262626</v>
       </c>
       <c r="S9" t="n">
-        <v>403.3021336040514</v>
+        <v>465.2525252525252</v>
       </c>
       <c r="T9" t="n">
-        <v>401.4545053111558</v>
+        <v>463.4048969596296</v>
       </c>
       <c r="U9" t="n">
-        <v>401.3001968055355</v>
+        <v>463.2505884540093</v>
       </c>
       <c r="V9" t="n">
-        <v>386.6429572181414</v>
+        <v>260.4376065764804</v>
       </c>
       <c r="W9" t="n">
-        <v>353.9428128647793</v>
+        <v>227.7374622231183</v>
       </c>
       <c r="X9" t="n">
-        <v>256.1737373737374</v>
+        <v>207.6740890459591</v>
       </c>
       <c r="Y9" t="n">
-        <v>256.1737373737374</v>
+        <v>207.6740890459591</v>
       </c>
     </row>
     <row r="10">
@@ -4929,13 +4929,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>35.25401294753327</v>
+        <v>18.8</v>
       </c>
       <c r="C10" t="n">
-        <v>35.25401294753327</v>
+        <v>18.8</v>
       </c>
       <c r="D10" t="n">
-        <v>35.25401294753327</v>
+        <v>18.8</v>
       </c>
       <c r="E10" t="n">
         <v>18.8</v>
@@ -4977,28 +4977,28 @@
         <v>35.25401294753327</v>
       </c>
       <c r="R10" t="n">
-        <v>35.25401294753327</v>
+        <v>18.8</v>
       </c>
       <c r="S10" t="n">
-        <v>35.25401294753327</v>
+        <v>18.8</v>
       </c>
       <c r="T10" t="n">
-        <v>35.25401294753327</v>
+        <v>18.8</v>
       </c>
       <c r="U10" t="n">
-        <v>35.25401294753327</v>
+        <v>18.8</v>
       </c>
       <c r="V10" t="n">
-        <v>35.25401294753327</v>
+        <v>18.8</v>
       </c>
       <c r="W10" t="n">
-        <v>35.25401294753327</v>
+        <v>18.8</v>
       </c>
       <c r="X10" t="n">
-        <v>35.25401294753327</v>
+        <v>18.8</v>
       </c>
       <c r="Y10" t="n">
-        <v>35.25401294753327</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="11">
@@ -5008,25 +5008,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>400.2639505907645</v>
+        <v>472.2436933726856</v>
       </c>
       <c r="C11" t="n">
-        <v>400.2639505907645</v>
+        <v>234.8699559989483</v>
       </c>
       <c r="D11" t="n">
-        <v>400.2639505907645</v>
+        <v>234.8699559989483</v>
       </c>
       <c r="E11" t="n">
-        <v>400.2639505907645</v>
+        <v>234.8699559989483</v>
       </c>
       <c r="F11" t="n">
-        <v>400.2639505907645</v>
+        <v>234.8699559989483</v>
       </c>
       <c r="G11" t="n">
-        <v>400.2639505907645</v>
+        <v>18.8</v>
       </c>
       <c r="H11" t="n">
-        <v>162.8902132170271</v>
+        <v>18.8</v>
       </c>
       <c r="I11" t="n">
         <v>18.8</v>
@@ -5044,40 +5044,40 @@
         <v>366.382509663657</v>
       </c>
       <c r="N11" t="n">
-        <v>225.1110816191458</v>
+        <v>244.866238124663</v>
       </c>
       <c r="O11" t="n">
-        <v>428.4869853639098</v>
+        <v>448.242141869427</v>
       </c>
       <c r="P11" t="n">
-        <v>661.1348066271528</v>
+        <v>680.8899631326699</v>
       </c>
       <c r="Q11" t="n">
-        <v>664.9625884896759</v>
+        <v>684.717744995193</v>
       </c>
       <c r="R11" t="n">
-        <v>664.9625884896759</v>
+        <v>684.717744995193</v>
       </c>
       <c r="S11" t="n">
-        <v>427.5888511159385</v>
+        <v>684.717744995193</v>
       </c>
       <c r="T11" t="n">
-        <v>427.5888511159385</v>
+        <v>684.717744995193</v>
       </c>
       <c r="U11" t="n">
-        <v>427.5888511159385</v>
+        <v>472.2436933726856</v>
       </c>
       <c r="V11" t="n">
-        <v>427.5888511159385</v>
+        <v>472.2436933726856</v>
       </c>
       <c r="W11" t="n">
-        <v>427.5888511159385</v>
+        <v>472.2436933726856</v>
       </c>
       <c r="X11" t="n">
-        <v>427.5888511159385</v>
+        <v>472.2436933726856</v>
       </c>
       <c r="Y11" t="n">
-        <v>400.2639505907645</v>
+        <v>472.2436933726856</v>
       </c>
     </row>
     <row r="12">
@@ -5087,13 +5087,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20.42966098822322</v>
+        <v>18.8</v>
       </c>
       <c r="C12" t="n">
-        <v>20.42966098822322</v>
+        <v>18.8</v>
       </c>
       <c r="D12" t="n">
-        <v>20.42966098822322</v>
+        <v>18.8</v>
       </c>
       <c r="E12" t="n">
         <v>18.8</v>
@@ -5144,19 +5144,19 @@
         <v>257.8033983619606</v>
       </c>
       <c r="U12" t="n">
-        <v>257.8033983619606</v>
+        <v>225.8185181302325</v>
       </c>
       <c r="V12" t="n">
-        <v>257.8033983619606</v>
+        <v>225.8185181302325</v>
       </c>
       <c r="W12" t="n">
-        <v>257.8033983619606</v>
+        <v>225.8185181302325</v>
       </c>
       <c r="X12" t="n">
-        <v>257.8033983619606</v>
+        <v>225.8185181302325</v>
       </c>
       <c r="Y12" t="n">
-        <v>257.8033983619606</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="13">
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>540.7327960984128</v>
+        <v>227.8787878787878</v>
       </c>
       <c r="C14" t="n">
-        <v>540.7327960984128</v>
+        <v>193.6698902853471</v>
       </c>
       <c r="D14" t="n">
-        <v>357.5619317147261</v>
+        <v>193.6698902853471</v>
       </c>
       <c r="E14" t="n">
-        <v>357.5619317147261</v>
+        <v>193.6698902853471</v>
       </c>
       <c r="F14" t="n">
-        <v>357.5619317147261</v>
+        <v>193.6698902853471</v>
       </c>
       <c r="G14" t="n">
-        <v>182.692041429379</v>
+        <v>18.8</v>
       </c>
       <c r="H14" t="n">
         <v>18.8</v>
@@ -5278,7 +5278,7 @@
         <v>560.2846080384661</v>
       </c>
       <c r="M14" t="n">
-        <v>532.0390753202227</v>
+        <v>500.1484931294698</v>
       </c>
       <c r="N14" t="n">
         <v>500.1484931294698</v>
@@ -5296,25 +5296,25 @@
         <v>940</v>
       </c>
       <c r="S14" t="n">
-        <v>709.1275803631173</v>
+        <v>940</v>
       </c>
       <c r="T14" t="n">
-        <v>709.1275803631173</v>
+        <v>702.6262626262626</v>
       </c>
       <c r="U14" t="n">
-        <v>709.1275803631173</v>
+        <v>702.6262626262626</v>
       </c>
       <c r="V14" t="n">
-        <v>709.1275803631173</v>
+        <v>702.6262626262626</v>
       </c>
       <c r="W14" t="n">
-        <v>540.7327960984128</v>
+        <v>465.2525252525252</v>
       </c>
       <c r="X14" t="n">
-        <v>540.7327960984128</v>
+        <v>465.2525252525252</v>
       </c>
       <c r="Y14" t="n">
-        <v>540.7327960984128</v>
+        <v>465.2525252525252</v>
       </c>
     </row>
     <row r="15">
@@ -5324,76 +5324,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>323.0561438186439</v>
+        <v>384.1271128091907</v>
       </c>
       <c r="C15" t="n">
-        <v>323.0561438186439</v>
+        <v>250.6928578137167</v>
       </c>
       <c r="D15" t="n">
-        <v>323.0561438186439</v>
+        <v>130.5537801392696</v>
       </c>
       <c r="E15" t="n">
-        <v>323.0561438186439</v>
+        <v>130.5537801392696</v>
       </c>
       <c r="F15" t="n">
-        <v>211.3023636793743</v>
+        <v>18.8</v>
       </c>
       <c r="G15" t="n">
-        <v>114.469937504866</v>
+        <v>18.8</v>
       </c>
       <c r="H15" t="n">
         <v>18.8</v>
       </c>
       <c r="I15" t="n">
-        <v>18.8</v>
+        <v>42.84419925245174</v>
       </c>
       <c r="J15" t="n">
-        <v>208.5955110896926</v>
+        <v>42.84419925245174</v>
       </c>
       <c r="K15" t="n">
-        <v>244.816641654221</v>
+        <v>163.5095198460839</v>
       </c>
       <c r="L15" t="n">
-        <v>477.466641654221</v>
+        <v>282.6859637731241</v>
       </c>
       <c r="M15" t="n">
-        <v>477.466641654221</v>
+        <v>348.095483290177</v>
       </c>
       <c r="N15" t="n">
-        <v>582.3114095508317</v>
+        <v>452.9402511867877</v>
       </c>
       <c r="O15" t="n">
-        <v>685.5902511867871</v>
+        <v>685.5902511867878</v>
       </c>
       <c r="P15" t="n">
-        <v>746.6581865945271</v>
+        <v>746.6581865945278</v>
       </c>
       <c r="Q15" t="n">
-        <v>895.54816434976</v>
+        <v>895.5481643497607</v>
       </c>
       <c r="R15" t="n">
-        <v>895.54816434976</v>
+        <v>782.2405977463478</v>
       </c>
       <c r="S15" t="n">
-        <v>895.54816434976</v>
+        <v>558.7020138293591</v>
       </c>
       <c r="T15" t="n">
-        <v>720.9732633295916</v>
+        <v>384.1271128091907</v>
       </c>
       <c r="U15" t="n">
-        <v>720.9732633295916</v>
+        <v>384.1271128091907</v>
       </c>
       <c r="V15" t="n">
-        <v>687.959307668666</v>
+        <v>384.1271128091907</v>
       </c>
       <c r="W15" t="n">
-        <v>687.959307668666</v>
+        <v>384.1271128091907</v>
       </c>
       <c r="X15" t="n">
-        <v>495.1686617642341</v>
+        <v>384.1271128091907</v>
       </c>
       <c r="Y15" t="n">
-        <v>323.0561438186439</v>
+        <v>384.1271128091907</v>
       </c>
     </row>
     <row r="16">
@@ -5418,28 +5418,28 @@
         <v>104.2820893703973</v>
       </c>
       <c r="G16" t="n">
-        <v>104.2820893703973</v>
+        <v>88.81750511251798</v>
       </c>
       <c r="H16" t="n">
-        <v>110.968765349467</v>
+        <v>95.50418109158768</v>
       </c>
       <c r="I16" t="n">
-        <v>162.5394985274945</v>
+        <v>147.0749142696152</v>
       </c>
       <c r="J16" t="n">
-        <v>395.1894985274945</v>
+        <v>379.7249142696152</v>
       </c>
       <c r="K16" t="n">
-        <v>420.6810701692809</v>
+        <v>405.2164859114015</v>
       </c>
       <c r="L16" t="n">
-        <v>420.6810701692809</v>
+        <v>405.2164859114015</v>
       </c>
       <c r="M16" t="n">
-        <v>242.3133388303912</v>
+        <v>405.2164859114015</v>
       </c>
       <c r="N16" t="n">
-        <v>18.8</v>
+        <v>173.0214438254142</v>
       </c>
       <c r="O16" t="n">
         <v>18.8</v>
@@ -5482,22 +5482,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18.8</v>
+        <v>710.1376813732184</v>
       </c>
       <c r="C17" t="n">
-        <v>18.8</v>
+        <v>710.1376813732184</v>
       </c>
       <c r="D17" t="n">
-        <v>18.8</v>
+        <v>527.9769179996326</v>
       </c>
       <c r="E17" t="n">
-        <v>18.8</v>
+        <v>351.8523830431997</v>
       </c>
       <c r="F17" t="n">
-        <v>18.8</v>
+        <v>351.8523830431997</v>
       </c>
       <c r="G17" t="n">
-        <v>18.8</v>
+        <v>181.681940419278</v>
       </c>
       <c r="H17" t="n">
         <v>18.8</v>
@@ -5515,7 +5515,7 @@
         <v>560.2846080384661</v>
       </c>
       <c r="M17" t="n">
-        <v>533.0491763303237</v>
+        <v>500.1484931294698</v>
       </c>
       <c r="N17" t="n">
         <v>500.1484931294698</v>
@@ -5536,22 +5536,22 @@
         <v>710.1376813732184</v>
       </c>
       <c r="T17" t="n">
-        <v>472.7639439994809</v>
+        <v>710.1376813732184</v>
       </c>
       <c r="U17" t="n">
-        <v>256.1737373737374</v>
+        <v>710.1376813732184</v>
       </c>
       <c r="V17" t="n">
-        <v>18.8</v>
+        <v>710.1376813732184</v>
       </c>
       <c r="W17" t="n">
-        <v>18.8</v>
+        <v>710.1376813732184</v>
       </c>
       <c r="X17" t="n">
-        <v>18.8</v>
+        <v>710.1376813732184</v>
       </c>
       <c r="Y17" t="n">
-        <v>18.8</v>
+        <v>710.1376813732184</v>
       </c>
     </row>
     <row r="18">
@@ -5561,76 +5561,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>265.0343531994262</v>
+        <v>475.7566462736527</v>
       </c>
       <c r="C18" t="n">
-        <v>132.6101992140532</v>
+        <v>343.3324922882797</v>
       </c>
       <c r="D18" t="n">
-        <v>132.6101992140532</v>
+        <v>224.2035156239336</v>
       </c>
       <c r="E18" t="n">
-        <v>18.8</v>
+        <v>224.2035156239336</v>
       </c>
       <c r="F18" t="n">
-        <v>18.8</v>
+        <v>113.459836494765</v>
       </c>
       <c r="G18" t="n">
-        <v>18.8</v>
+        <v>113.459836494765</v>
       </c>
       <c r="H18" t="n">
         <v>18.8</v>
       </c>
       <c r="I18" t="n">
-        <v>43.83419925245174</v>
+        <v>61.38450532605552</v>
       </c>
       <c r="J18" t="n">
-        <v>252.1828431267874</v>
+        <v>61.38450532605552</v>
       </c>
       <c r="K18" t="n">
-        <v>288.4039736913157</v>
+        <v>97.60563589058386</v>
       </c>
       <c r="L18" t="n">
-        <v>363.725705870561</v>
+        <v>172.9273680698292</v>
       </c>
       <c r="M18" t="n">
-        <v>547.6731110090278</v>
+        <v>356.2347738243101</v>
       </c>
       <c r="N18" t="n">
-        <v>653.5078789056386</v>
+        <v>462.0695417209209</v>
       </c>
       <c r="O18" t="n">
-        <v>719.9004791160854</v>
+        <v>694.7195417209209</v>
       </c>
       <c r="P18" t="n">
-        <v>780.9684145238255</v>
+        <v>755.787477128661</v>
       </c>
       <c r="Q18" t="n">
-        <v>930.8483922790583</v>
+        <v>922.7698982739919</v>
       </c>
       <c r="R18" t="n">
-        <v>930.8483922790583</v>
+        <v>922.7698982739919</v>
       </c>
       <c r="S18" t="n">
-        <v>930.8483922790583</v>
+        <v>700.2414153671041</v>
       </c>
       <c r="T18" t="n">
-        <v>930.8483922790583</v>
+        <v>526.6766153570368</v>
       </c>
       <c r="U18" t="n">
-        <v>758.9769120562663</v>
+        <v>526.6766153570368</v>
       </c>
       <c r="V18" t="n">
-        <v>572.6025007517005</v>
+        <v>475.7566462736527</v>
       </c>
       <c r="W18" t="n">
-        <v>572.6025007517005</v>
+        <v>475.7566462736527</v>
       </c>
       <c r="X18" t="n">
-        <v>436.1367701349154</v>
+        <v>475.7566462736527</v>
       </c>
       <c r="Y18" t="n">
-        <v>265.0343531994262</v>
+        <v>475.7566462736527</v>
       </c>
     </row>
     <row r="19">
@@ -5640,13 +5640,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>106.7879824401885</v>
+        <v>214.3810358669683</v>
       </c>
       <c r="C19" t="n">
-        <v>63.63116764418378</v>
+        <v>171.2242210709636</v>
       </c>
       <c r="D19" t="n">
-        <v>63.63116764418378</v>
+        <v>115.1270311158571</v>
       </c>
       <c r="E19" t="n">
         <v>63.63116764418378</v>
@@ -5661,55 +5661,55 @@
         <v>26.4766759790697</v>
       </c>
       <c r="I19" t="n">
-        <v>86.88824457723896</v>
+        <v>101.1602506528575</v>
       </c>
       <c r="J19" t="n">
-        <v>319.538244577239</v>
+        <v>333.8102506528576</v>
       </c>
       <c r="K19" t="n">
-        <v>346.0198162190254</v>
+        <v>360.291822294644</v>
       </c>
       <c r="L19" t="n">
-        <v>260.7353764504456</v>
+        <v>360.291822294644</v>
       </c>
       <c r="M19" t="n">
-        <v>260.7353764504456</v>
+        <v>360.291822294644</v>
       </c>
       <c r="N19" t="n">
-        <v>29.55043537455928</v>
+        <v>360.291822294644</v>
       </c>
       <c r="O19" t="n">
-        <v>29.55043537455928</v>
+        <v>360.291822294644</v>
       </c>
       <c r="P19" t="n">
-        <v>29.55043537455928</v>
+        <v>360.291822294644</v>
       </c>
       <c r="Q19" t="n">
-        <v>29.55043537455928</v>
+        <v>360.291822294644</v>
       </c>
       <c r="R19" t="n">
-        <v>29.55043537455928</v>
+        <v>122.9180849209066</v>
       </c>
       <c r="S19" t="n">
-        <v>29.55043537455928</v>
+        <v>122.9180849209066</v>
       </c>
       <c r="T19" t="n">
-        <v>52.43065715631496</v>
+        <v>145.7983067026623</v>
       </c>
       <c r="U19" t="n">
-        <v>130.721482253618</v>
+        <v>224.0891317999653</v>
       </c>
       <c r="V19" t="n">
-        <v>161.242875139564</v>
+        <v>254.6105246859113</v>
       </c>
       <c r="W19" t="n">
-        <v>164.8337933992414</v>
+        <v>258.2014429455887</v>
       </c>
       <c r="X19" t="n">
-        <v>164.8337933992414</v>
+        <v>258.2014429455887</v>
       </c>
       <c r="Y19" t="n">
-        <v>106.7879824401885</v>
+        <v>258.2014429455887</v>
       </c>
     </row>
     <row r="20">
@@ -5719,22 +5719,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>599.3084471624804</v>
+        <v>702.6262626262626</v>
       </c>
       <c r="C20" t="n">
-        <v>377.6169539877391</v>
+        <v>702.6262626262626</v>
       </c>
       <c r="D20" t="n">
-        <v>195.4561906141534</v>
+        <v>534.4626659898644</v>
       </c>
       <c r="E20" t="n">
-        <v>195.4561906141534</v>
+        <v>358.3381310334314</v>
       </c>
       <c r="F20" t="n">
-        <v>18.8</v>
+        <v>181.681940419278</v>
       </c>
       <c r="G20" t="n">
-        <v>18.8</v>
+        <v>181.681940419278</v>
       </c>
       <c r="H20" t="n">
         <v>18.8</v>
@@ -5752,7 +5752,7 @@
         <v>560.2846080384661</v>
       </c>
       <c r="M20" t="n">
-        <v>533.0491763303237</v>
+        <v>500.1484931294698</v>
       </c>
       <c r="N20" t="n">
         <v>500.1484931294698</v>
@@ -5788,7 +5788,7 @@
         <v>940</v>
       </c>
       <c r="Y20" t="n">
-        <v>836.6821845362178</v>
+        <v>940</v>
       </c>
     </row>
     <row r="21">
@@ -5798,19 +5798,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>245.883990480138</v>
+        <v>685.3891706521131</v>
       </c>
       <c r="C21" t="n">
-        <v>113.459836494765</v>
+        <v>552.9650166667401</v>
       </c>
       <c r="D21" t="n">
-        <v>113.459836494765</v>
+        <v>433.836040002394</v>
       </c>
       <c r="E21" t="n">
-        <v>113.459836494765</v>
+        <v>320.0258407883408</v>
       </c>
       <c r="F21" t="n">
-        <v>113.459836494765</v>
+        <v>209.2821616591723</v>
       </c>
       <c r="G21" t="n">
         <v>113.459836494765</v>
@@ -5819,55 +5819,55 @@
         <v>18.8</v>
       </c>
       <c r="I21" t="n">
-        <v>43.83419925245175</v>
+        <v>43.83419925245174</v>
       </c>
       <c r="J21" t="n">
-        <v>252.1828431267874</v>
+        <v>43.83419925245174</v>
       </c>
       <c r="K21" t="n">
-        <v>288.4039736913157</v>
+        <v>80.05532981698008</v>
       </c>
       <c r="L21" t="n">
-        <v>429.1884783337175</v>
+        <v>155.3770619962254</v>
       </c>
       <c r="M21" t="n">
-        <v>495.5879978507704</v>
+        <v>221.7765815132782</v>
       </c>
       <c r="N21" t="n">
-        <v>495.5879978507704</v>
+        <v>327.611349409889</v>
       </c>
       <c r="O21" t="n">
-        <v>728.2379978507704</v>
+        <v>560.261349409889</v>
       </c>
       <c r="P21" t="n">
-        <v>789.3059332585104</v>
+        <v>784.9606449684711</v>
       </c>
       <c r="Q21" t="n">
-        <v>939.1859110137433</v>
+        <v>934.840622723704</v>
       </c>
       <c r="R21" t="n">
-        <v>939.1859110137433</v>
+        <v>934.840622723704</v>
       </c>
       <c r="S21" t="n">
-        <v>939.1859110137433</v>
+        <v>934.840622723704</v>
       </c>
       <c r="T21" t="n">
-        <v>795.9104269018267</v>
+        <v>857.2606508749051</v>
       </c>
       <c r="U21" t="n">
-        <v>624.0389466790347</v>
+        <v>685.3891706521131</v>
       </c>
       <c r="V21" t="n">
-        <v>437.6645353744689</v>
+        <v>685.3891706521131</v>
       </c>
       <c r="W21" t="n">
-        <v>437.6645353744689</v>
+        <v>685.3891706521131</v>
       </c>
       <c r="X21" t="n">
-        <v>245.883990480138</v>
+        <v>685.3891706521131</v>
       </c>
       <c r="Y21" t="n">
-        <v>245.883990480138</v>
+        <v>685.3891706521131</v>
       </c>
     </row>
     <row r="22">
@@ -5886,43 +5886,43 @@
         <v>154.0833580246821</v>
       </c>
       <c r="E22" t="n">
-        <v>102.5874945530088</v>
+        <v>154.0833580246821</v>
       </c>
       <c r="F22" t="n">
-        <v>102.5874945530088</v>
+        <v>154.0833580246821</v>
       </c>
       <c r="G22" t="n">
-        <v>88.1330113052305</v>
+        <v>139.6288747769038</v>
       </c>
       <c r="H22" t="n">
-        <v>88.1330113052305</v>
+        <v>147.3055507559735</v>
       </c>
       <c r="I22" t="n">
-        <v>162.8165859790183</v>
+        <v>221.9891254297613</v>
       </c>
       <c r="J22" t="n">
-        <v>374.1416394511947</v>
+        <v>433.314178901937</v>
       </c>
       <c r="K22" t="n">
-        <v>400.6232110929811</v>
+        <v>459.7957505437234</v>
       </c>
       <c r="L22" t="n">
-        <v>400.6232110929811</v>
+        <v>459.7957505437234</v>
       </c>
       <c r="M22" t="n">
-        <v>400.6232110929811</v>
+        <v>459.7957505437234</v>
       </c>
       <c r="N22" t="n">
-        <v>400.6232110929811</v>
+        <v>459.7957505437234</v>
       </c>
       <c r="O22" t="n">
-        <v>400.6232110929811</v>
+        <v>459.7957505437234</v>
       </c>
       <c r="P22" t="n">
-        <v>400.6232110929811</v>
+        <v>459.7957505437234</v>
       </c>
       <c r="Q22" t="n">
-        <v>376.9646508010297</v>
+        <v>222.422013169986</v>
       </c>
       <c r="R22" t="n">
         <v>139.5909134272923</v>
@@ -5931,7 +5931,7 @@
         <v>18.8</v>
       </c>
       <c r="T22" t="n">
-        <v>41.68022178175569</v>
+        <v>41.68022178175568</v>
       </c>
       <c r="U22" t="n">
         <v>119.9710468790587</v>
@@ -5956,22 +5956,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>465.2525252525252</v>
+        <v>756.1541591646057</v>
       </c>
       <c r="C23" t="n">
-        <v>465.2525252525252</v>
+        <v>534.4626659898644</v>
       </c>
       <c r="D23" t="n">
-        <v>283.0917618789395</v>
+        <v>534.4626659898644</v>
       </c>
       <c r="E23" t="n">
-        <v>283.0917618789395</v>
+        <v>358.3381310334314</v>
       </c>
       <c r="F23" t="n">
-        <v>106.4355712647861</v>
+        <v>181.681940419278</v>
       </c>
       <c r="G23" t="n">
-        <v>18.8</v>
+        <v>181.681940419278</v>
       </c>
       <c r="H23" t="n">
         <v>18.8</v>
@@ -5989,7 +5989,7 @@
         <v>560.2846080384661</v>
       </c>
       <c r="M23" t="n">
-        <v>560.2846080384661</v>
+        <v>500.1484931294698</v>
       </c>
       <c r="N23" t="n">
         <v>500.1484931294698</v>
@@ -6019,13 +6019,13 @@
         <v>940</v>
       </c>
       <c r="W23" t="n">
-        <v>702.6262626262626</v>
+        <v>940</v>
       </c>
       <c r="X23" t="n">
-        <v>702.6262626262626</v>
+        <v>940</v>
       </c>
       <c r="Y23" t="n">
-        <v>465.2525252525252</v>
+        <v>940</v>
       </c>
     </row>
     <row r="24">
@@ -6035,76 +6035,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>365.0129671444842</v>
+        <v>137.9289766643461</v>
       </c>
       <c r="C24" t="n">
-        <v>232.5888131591111</v>
+        <v>137.9289766643461</v>
       </c>
       <c r="D24" t="n">
-        <v>113.459836494765</v>
+        <v>18.8</v>
       </c>
       <c r="E24" t="n">
-        <v>113.459836494765</v>
+        <v>18.8</v>
       </c>
       <c r="F24" t="n">
-        <v>113.459836494765</v>
+        <v>18.8</v>
       </c>
       <c r="G24" t="n">
-        <v>113.459836494765</v>
+        <v>18.8</v>
       </c>
       <c r="H24" t="n">
         <v>18.8</v>
       </c>
       <c r="I24" t="n">
-        <v>43.83419925245175</v>
+        <v>43.83419925245174</v>
       </c>
       <c r="J24" t="n">
-        <v>43.83419925245175</v>
+        <v>252.1828431267874</v>
       </c>
       <c r="K24" t="n">
-        <v>276.4841992524517</v>
+        <v>288.4039736913157</v>
       </c>
       <c r="L24" t="n">
-        <v>509.1341992524517</v>
+        <v>363.725705870561</v>
       </c>
       <c r="M24" t="n">
-        <v>509.1341992524517</v>
+        <v>430.1252253876139</v>
       </c>
       <c r="N24" t="n">
-        <v>509.1341992524517</v>
+        <v>589.3919033255712</v>
       </c>
       <c r="O24" t="n">
-        <v>714.9652426421425</v>
+        <v>655.7845035360181</v>
       </c>
       <c r="P24" t="n">
-        <v>776.0331780498825</v>
+        <v>772.8899205187588</v>
       </c>
       <c r="Q24" t="n">
-        <v>925.9131558051154</v>
+        <v>922.7698982739917</v>
       </c>
       <c r="R24" t="n">
-        <v>925.9131558051154</v>
+        <v>685.3961609002542</v>
       </c>
       <c r="S24" t="n">
-        <v>881.5516643128328</v>
+        <v>685.3961609002542</v>
       </c>
       <c r="T24" t="n">
-        <v>707.9868643027654</v>
+        <v>511.8313608901869</v>
       </c>
       <c r="U24" t="n">
-        <v>536.1153840799734</v>
+        <v>480.4211219551004</v>
       </c>
       <c r="V24" t="n">
-        <v>536.1153840799734</v>
+        <v>294.0467106505346</v>
       </c>
       <c r="W24" t="n">
-        <v>536.1153840799734</v>
+        <v>294.0467106505346</v>
       </c>
       <c r="X24" t="n">
-        <v>536.1153840799734</v>
+        <v>294.0467106505346</v>
       </c>
       <c r="Y24" t="n">
-        <v>365.0129671444842</v>
+        <v>294.0467106505346</v>
       </c>
     </row>
     <row r="25">
@@ -6114,76 +6114,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>134.1828408470687</v>
+        <v>154.0833580246821</v>
       </c>
       <c r="C25" t="n">
-        <v>134.1828408470687</v>
+        <v>154.0833580246821</v>
       </c>
       <c r="D25" t="n">
-        <v>78.0856508919621</v>
+        <v>154.0833580246821</v>
       </c>
       <c r="E25" t="n">
-        <v>78.0856508919621</v>
+        <v>154.0833580246821</v>
       </c>
       <c r="F25" t="n">
-        <v>33.25448324777832</v>
+        <v>154.0833580246821</v>
       </c>
       <c r="G25" t="n">
+        <v>154.0833580246821</v>
+      </c>
+      <c r="H25" t="n">
+        <v>161.7600340037518</v>
+      </c>
+      <c r="I25" t="n">
+        <v>236.4436086775396</v>
+      </c>
+      <c r="J25" t="n">
+        <v>469.0936086775396</v>
+      </c>
+      <c r="K25" t="n">
+        <v>495.575180319326</v>
+      </c>
+      <c r="L25" t="n">
+        <v>495.575180319326</v>
+      </c>
+      <c r="M25" t="n">
+        <v>318.2175499905373</v>
+      </c>
+      <c r="N25" t="n">
+        <v>256.1737373737374</v>
+      </c>
+      <c r="O25" t="n">
+        <v>256.1737373737374</v>
+      </c>
+      <c r="P25" t="n">
+        <v>256.1737373737374</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>256.1737373737374</v>
+      </c>
+      <c r="R25" t="n">
         <v>18.8</v>
       </c>
-      <c r="H25" t="n">
-        <v>26.4766759790697</v>
-      </c>
-      <c r="I25" t="n">
-        <v>101.1602506528575</v>
-      </c>
-      <c r="J25" t="n">
-        <v>328.2571623478717</v>
-      </c>
-      <c r="K25" t="n">
-        <v>354.738733989658</v>
-      </c>
-      <c r="L25" t="n">
-        <v>354.738733989658</v>
-      </c>
-      <c r="M25" t="n">
-        <v>177.3811036608694</v>
-      </c>
-      <c r="N25" t="n">
-        <v>177.3811036608694</v>
-      </c>
-      <c r="O25" t="n">
-        <v>177.3811036608694</v>
-      </c>
-      <c r="P25" t="n">
-        <v>177.3811036608694</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>177.3811036608694</v>
-      </c>
-      <c r="R25" t="n">
-        <v>177.3811036608694</v>
-      </c>
       <c r="S25" t="n">
-        <v>56.59019023357713</v>
+        <v>18.8</v>
       </c>
       <c r="T25" t="n">
-        <v>79.47041201533283</v>
+        <v>41.68022178175568</v>
       </c>
       <c r="U25" t="n">
-        <v>157.7612371126359</v>
+        <v>119.9710468790587</v>
       </c>
       <c r="V25" t="n">
-        <v>188.2826299985818</v>
+        <v>150.4924397650047</v>
       </c>
       <c r="W25" t="n">
-        <v>191.8735482582592</v>
+        <v>154.0833580246821</v>
       </c>
       <c r="X25" t="n">
-        <v>191.8735482582592</v>
+        <v>154.0833580246821</v>
       </c>
       <c r="Y25" t="n">
-        <v>191.8735482582592</v>
+        <v>154.0833580246821</v>
       </c>
     </row>
     <row r="26">
@@ -6193,19 +6193,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>548</v>
+        <v>312.6259707927866</v>
       </c>
       <c r="C26" t="n">
-        <v>548</v>
+        <v>312.6259707927866</v>
       </c>
       <c r="D26" t="n">
-        <v>451.0098091766249</v>
+        <v>312.6259707927866</v>
       </c>
       <c r="E26" t="n">
-        <v>312.6259707927861</v>
+        <v>312.6259707927866</v>
       </c>
       <c r="F26" t="n">
-        <v>174.2421324089472</v>
+        <v>312.6259707927866</v>
       </c>
       <c r="G26" t="n">
         <v>174.2421324089472</v>
@@ -6226,7 +6226,7 @@
         <v>385.0075447721345</v>
       </c>
       <c r="M26" t="n">
-        <v>275.2365704845516</v>
+        <v>310.2973655892446</v>
       </c>
       <c r="N26" t="n">
         <v>272.9122181374768</v>
@@ -6247,22 +6247,22 @@
         <v>548</v>
       </c>
       <c r="T26" t="n">
-        <v>548</v>
+        <v>409.6161616161608</v>
       </c>
       <c r="U26" t="n">
-        <v>548</v>
+        <v>312.6259707927866</v>
       </c>
       <c r="V26" t="n">
-        <v>548</v>
+        <v>312.6259707927866</v>
       </c>
       <c r="W26" t="n">
-        <v>548</v>
+        <v>312.6259707927866</v>
       </c>
       <c r="X26" t="n">
-        <v>548</v>
+        <v>312.6259707927866</v>
       </c>
       <c r="Y26" t="n">
-        <v>548</v>
+        <v>312.6259707927866</v>
       </c>
     </row>
     <row r="27">
@@ -6272,13 +6272,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>171.276090957605</v>
+        <v>429.7919109065114</v>
       </c>
       <c r="C27" t="n">
-        <v>32.8922525737662</v>
+        <v>291.4080725226729</v>
       </c>
       <c r="D27" t="n">
-        <v>32.8922525737662</v>
+        <v>153.0242341388339</v>
       </c>
       <c r="E27" t="n">
         <v>32.8922525737662</v>
@@ -6296,52 +6296,52 @@
         <v>10.96</v>
       </c>
       <c r="J27" t="n">
-        <v>10.96</v>
+        <v>67.56901527226509</v>
       </c>
       <c r="K27" t="n">
-        <v>62.73723475895456</v>
+        <v>103.7901458367934</v>
       </c>
       <c r="L27" t="n">
-        <v>138.0589669381999</v>
+        <v>179.1118780160387</v>
       </c>
       <c r="M27" t="n">
-        <v>157.9284864552527</v>
+        <v>198.9813975330916</v>
       </c>
       <c r="N27" t="n">
-        <v>217.2332543518635</v>
+        <v>198.9813975330916</v>
       </c>
       <c r="O27" t="n">
-        <v>283.6258545623103</v>
+        <v>265.3739977435384</v>
       </c>
       <c r="P27" t="n">
-        <v>344.6937899700504</v>
+        <v>326.4419331512785</v>
       </c>
       <c r="Q27" t="n">
-        <v>448.0437677252833</v>
+        <v>429.7919109065114</v>
       </c>
       <c r="R27" t="n">
-        <v>448.0437677252833</v>
+        <v>429.7919109065114</v>
       </c>
       <c r="S27" t="n">
-        <v>448.0437677252833</v>
+        <v>429.7919109065114</v>
       </c>
       <c r="T27" t="n">
-        <v>448.0437677252833</v>
+        <v>429.7919109065114</v>
       </c>
       <c r="U27" t="n">
-        <v>309.6599293414438</v>
+        <v>429.7919109065114</v>
       </c>
       <c r="V27" t="n">
-        <v>309.6599293414438</v>
+        <v>429.7919109065114</v>
       </c>
       <c r="W27" t="n">
-        <v>309.6599293414438</v>
+        <v>429.7919109065114</v>
       </c>
       <c r="X27" t="n">
-        <v>309.6599293414438</v>
+        <v>429.7919109065114</v>
       </c>
       <c r="Y27" t="n">
-        <v>171.276090957605</v>
+        <v>429.7919109065114</v>
       </c>
     </row>
     <row r="28">
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>42.72082509730302</v>
+        <v>29.2427278625486</v>
       </c>
       <c r="C28" t="n">
-        <v>42.72082509730302</v>
+        <v>29.2427278625486</v>
       </c>
       <c r="D28" t="n">
-        <v>42.72082509730302</v>
+        <v>29.2427278625486</v>
       </c>
       <c r="E28" t="n">
-        <v>42.72082509730302</v>
+        <v>29.2427278625486</v>
       </c>
       <c r="F28" t="n">
-        <v>42.72082509730302</v>
+        <v>29.2427278625486</v>
       </c>
       <c r="G28" t="n">
-        <v>42.72082509730302</v>
+        <v>29.2427278625486</v>
       </c>
       <c r="H28" t="n">
-        <v>42.72082509730302</v>
+        <v>10.96</v>
       </c>
       <c r="I28" t="n">
-        <v>48.75155827533055</v>
+        <v>16.99073317802753</v>
       </c>
       <c r="J28" t="n">
-        <v>81.27231104013293</v>
+        <v>81.7564329893257</v>
       </c>
       <c r="K28" t="n">
-        <v>81.27231104013293</v>
+        <v>81.7564329893257</v>
       </c>
       <c r="L28" t="n">
-        <v>81.27231104013293</v>
+        <v>81.7564329893257</v>
       </c>
       <c r="M28" t="n">
-        <v>81.27231104013293</v>
+        <v>81.7564329893257</v>
       </c>
       <c r="N28" t="n">
-        <v>81.27231104013293</v>
+        <v>81.7564329893257</v>
       </c>
       <c r="O28" t="n">
-        <v>81.27231104013293</v>
+        <v>81.7564329893257</v>
       </c>
       <c r="P28" t="n">
-        <v>81.27231104013293</v>
+        <v>81.7564329893257</v>
       </c>
       <c r="Q28" t="n">
-        <v>81.27231104013293</v>
+        <v>81.7564329893257</v>
       </c>
       <c r="R28" t="n">
-        <v>35.08996451203379</v>
+        <v>81.7564329893257</v>
       </c>
       <c r="S28" t="n">
-        <v>35.08996451203379</v>
+        <v>81.7564329893257</v>
       </c>
       <c r="T28" t="n">
-        <v>10.96</v>
+        <v>57.62646847729192</v>
       </c>
       <c r="U28" t="n">
-        <v>42.72082509730302</v>
+        <v>89.38729357459495</v>
       </c>
       <c r="V28" t="n">
-        <v>42.72082509730302</v>
+        <v>73.05364689154828</v>
       </c>
       <c r="W28" t="n">
-        <v>42.72082509730302</v>
+        <v>29.2427278625486</v>
       </c>
       <c r="X28" t="n">
-        <v>42.72082509730302</v>
+        <v>29.2427278625486</v>
       </c>
       <c r="Y28" t="n">
-        <v>42.72082509730302</v>
+        <v>29.2427278625486</v>
       </c>
     </row>
     <row r="29">
@@ -6430,19 +6430,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>548</v>
+        <v>287.7276767676785</v>
       </c>
       <c r="C29" t="n">
-        <v>409.6161616161608</v>
+        <v>149.3438383838397</v>
       </c>
       <c r="D29" t="n">
-        <v>271.2323232323216</v>
+        <v>149.3438383838397</v>
       </c>
       <c r="E29" t="n">
-        <v>132.8484848484825</v>
+        <v>149.3438383838397</v>
       </c>
       <c r="F29" t="n">
-        <v>132.8484848484825</v>
+        <v>149.3438383838397</v>
       </c>
       <c r="G29" t="n">
         <v>10.96</v>
@@ -6466,10 +6466,10 @@
         <v>328.4791837710628</v>
       </c>
       <c r="N29" t="n">
-        <v>272.9122181374763</v>
+        <v>272.9122181374765</v>
       </c>
       <c r="O29" t="n">
-        <v>408.5422181374766</v>
+        <v>408.5422181374767</v>
       </c>
       <c r="P29" t="n">
         <v>544.1722181374769</v>
@@ -6487,19 +6487,19 @@
         <v>548</v>
       </c>
       <c r="U29" t="n">
-        <v>548</v>
+        <v>409.6161616161603</v>
       </c>
       <c r="V29" t="n">
-        <v>548</v>
+        <v>409.6161616161603</v>
       </c>
       <c r="W29" t="n">
-        <v>548</v>
+        <v>409.6161616161603</v>
       </c>
       <c r="X29" t="n">
-        <v>548</v>
+        <v>287.7276767676785</v>
       </c>
       <c r="Y29" t="n">
-        <v>548</v>
+        <v>287.7276767676785</v>
       </c>
     </row>
     <row r="30">
@@ -6509,19 +6509,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>273.2966041715334</v>
+        <v>260.0280202450309</v>
       </c>
       <c r="C30" t="n">
-        <v>273.2966041715334</v>
+        <v>260.0280202450309</v>
       </c>
       <c r="D30" t="n">
-        <v>273.2966041715334</v>
+        <v>260.0280202450309</v>
       </c>
       <c r="E30" t="n">
-        <v>273.2966041715334</v>
+        <v>260.0280202450309</v>
       </c>
       <c r="F30" t="n">
-        <v>134.9127657876943</v>
+        <v>260.0280202450309</v>
       </c>
       <c r="G30" t="n">
         <v>134.9127657876943</v>
@@ -6533,52 +6533,52 @@
         <v>10.96</v>
       </c>
       <c r="J30" t="n">
-        <v>25.56328432554562</v>
+        <v>48.18203262924703</v>
       </c>
       <c r="K30" t="n">
-        <v>161.1932843255456</v>
+        <v>183.812032629247</v>
       </c>
       <c r="L30" t="n">
-        <v>296.8232843255456</v>
+        <v>259.1337648084923</v>
       </c>
       <c r="M30" t="n">
-        <v>296.8232843255456</v>
+        <v>296.8232843255452</v>
       </c>
       <c r="N30" t="n">
-        <v>296.8232843255456</v>
+        <v>296.8232843255452</v>
       </c>
       <c r="O30" t="n">
-        <v>363.2158845359925</v>
+        <v>363.2158845359921</v>
       </c>
       <c r="P30" t="n">
-        <v>424.2838199437326</v>
+        <v>424.2838199437322</v>
       </c>
       <c r="Q30" t="n">
-        <v>545.4537976989654</v>
+        <v>545.453797698965</v>
       </c>
       <c r="R30" t="n">
-        <v>545.4537976989654</v>
+        <v>545.453797698965</v>
       </c>
       <c r="S30" t="n">
-        <v>545.4537976989654</v>
+        <v>545.453797698965</v>
       </c>
       <c r="T30" t="n">
-        <v>545.4537976989654</v>
+        <v>545.453797698965</v>
       </c>
       <c r="U30" t="n">
-        <v>545.4537976989654</v>
+        <v>407.0699593151255</v>
       </c>
       <c r="V30" t="n">
-        <v>545.4537976989654</v>
+        <v>268.6861209312866</v>
       </c>
       <c r="W30" t="n">
-        <v>545.4537976989654</v>
+        <v>268.6861209312866</v>
       </c>
       <c r="X30" t="n">
-        <v>545.4537976989654</v>
+        <v>268.6861209312866</v>
       </c>
       <c r="Y30" t="n">
-        <v>411.6804425553725</v>
+        <v>268.6861209312866</v>
       </c>
     </row>
     <row r="31">
@@ -6588,76 +6588,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>62.35221798324901</v>
+        <v>58.2345187771964</v>
       </c>
       <c r="C31" t="n">
-        <v>62.35221798324901</v>
+        <v>58.2345187771964</v>
       </c>
       <c r="D31" t="n">
-        <v>62.35221798324901</v>
+        <v>32.4203856962864</v>
       </c>
       <c r="E31" t="n">
-        <v>62.35221798324901</v>
+        <v>32.4203856962864</v>
       </c>
       <c r="F31" t="n">
-        <v>62.35221798324901</v>
+        <v>32.4203856962864</v>
       </c>
       <c r="G31" t="n">
-        <v>62.35221798324901</v>
+        <v>32.4203856962864</v>
       </c>
       <c r="H31" t="n">
-        <v>40.89183228696261</v>
+        <v>10.96</v>
       </c>
       <c r="I31" t="n">
-        <v>86.86540696075045</v>
+        <v>56.93357467378783</v>
       </c>
       <c r="J31" t="n">
-        <v>206.7352186421459</v>
+        <v>176.8033863551829</v>
       </c>
       <c r="K31" t="n">
-        <v>206.7352186421459</v>
+        <v>176.8033863551829</v>
       </c>
       <c r="L31" t="n">
-        <v>149.3438383838384</v>
+        <v>176.8033863551829</v>
       </c>
       <c r="M31" t="n">
-        <v>149.3438383838384</v>
+        <v>176.8033863551829</v>
       </c>
       <c r="N31" t="n">
-        <v>149.3438383838384</v>
+        <v>176.8033863551829</v>
       </c>
       <c r="O31" t="n">
-        <v>149.3438383838384</v>
+        <v>176.8033863551829</v>
       </c>
       <c r="P31" t="n">
-        <v>149.3438383838384</v>
+        <v>176.8033863551829</v>
       </c>
       <c r="Q31" t="n">
-        <v>149.3438383838384</v>
+        <v>176.8033863551829</v>
       </c>
       <c r="R31" t="n">
-        <v>10.96</v>
+        <v>176.8033863551829</v>
       </c>
       <c r="S31" t="n">
-        <v>10.96</v>
+        <v>38.41954797134451</v>
       </c>
       <c r="T31" t="n">
-        <v>10.96</v>
+        <v>32.47140164112891</v>
       </c>
       <c r="U31" t="n">
-        <v>60.54082509730303</v>
+        <v>82.05222673843194</v>
       </c>
       <c r="V31" t="n">
-        <v>62.35221798324901</v>
+        <v>83.8636196243779</v>
       </c>
       <c r="W31" t="n">
-        <v>62.35221798324901</v>
+        <v>58.2345187771964</v>
       </c>
       <c r="X31" t="n">
-        <v>62.35221798324901</v>
+        <v>58.2345187771964</v>
       </c>
       <c r="Y31" t="n">
-        <v>62.35221798324901</v>
+        <v>58.2345187771964</v>
       </c>
     </row>
     <row r="32">
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>287.7276767676783</v>
+        <v>149.3438383838394</v>
       </c>
       <c r="C32" t="n">
-        <v>287.7276767676783</v>
+        <v>149.3438383838394</v>
       </c>
       <c r="D32" t="n">
         <v>149.3438383838394</v>
@@ -6718,25 +6718,25 @@
         <v>548</v>
       </c>
       <c r="S32" t="n">
-        <v>409.6161616161605</v>
+        <v>426.1115151515177</v>
       </c>
       <c r="T32" t="n">
-        <v>287.7276767676783</v>
+        <v>426.1115151515177</v>
       </c>
       <c r="U32" t="n">
-        <v>287.7276767676783</v>
+        <v>287.7276767676782</v>
       </c>
       <c r="V32" t="n">
-        <v>287.7276767676783</v>
+        <v>287.7276767676782</v>
       </c>
       <c r="W32" t="n">
-        <v>287.7276767676783</v>
+        <v>149.3438383838394</v>
       </c>
       <c r="X32" t="n">
-        <v>287.7276767676783</v>
+        <v>149.3438383838394</v>
       </c>
       <c r="Y32" t="n">
-        <v>287.7276767676783</v>
+        <v>149.3438383838394</v>
       </c>
     </row>
     <row r="33">
@@ -6746,19 +6746,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>407.0699593151251</v>
+        <v>10.96</v>
       </c>
       <c r="C33" t="n">
-        <v>407.0699593151251</v>
+        <v>10.96</v>
       </c>
       <c r="D33" t="n">
-        <v>407.0699593151251</v>
+        <v>10.96</v>
       </c>
       <c r="E33" t="n">
-        <v>268.6861209312861</v>
+        <v>10.96</v>
       </c>
       <c r="F33" t="n">
-        <v>130.3022825474472</v>
+        <v>10.96</v>
       </c>
       <c r="G33" t="n">
         <v>10.96</v>
@@ -6770,52 +6770,52 @@
         <v>10.96</v>
       </c>
       <c r="J33" t="n">
-        <v>146.59</v>
+        <v>10.96</v>
       </c>
       <c r="K33" t="n">
-        <v>196.3093622153688</v>
+        <v>47.18113056452834</v>
       </c>
       <c r="L33" t="n">
-        <v>271.6310943946141</v>
+        <v>182.0089969118816</v>
       </c>
       <c r="M33" t="n">
-        <v>271.6310943946141</v>
+        <v>219.6985164289344</v>
       </c>
       <c r="N33" t="n">
-        <v>348.7558622912248</v>
+        <v>296.8232843255452</v>
       </c>
       <c r="O33" t="n">
-        <v>484.3858622912248</v>
+        <v>363.215884535992</v>
       </c>
       <c r="P33" t="n">
-        <v>545.4537976989649</v>
+        <v>424.2838199437321</v>
       </c>
       <c r="Q33" t="n">
-        <v>545.4537976989649</v>
+        <v>545.453797698965</v>
       </c>
       <c r="R33" t="n">
-        <v>407.0699593151251</v>
+        <v>426.1115151515169</v>
       </c>
       <c r="S33" t="n">
-        <v>407.0699593151251</v>
+        <v>426.1115151515169</v>
       </c>
       <c r="T33" t="n">
-        <v>407.0699593151251</v>
+        <v>287.7276767676776</v>
       </c>
       <c r="U33" t="n">
-        <v>407.0699593151251</v>
+        <v>287.7276767676776</v>
       </c>
       <c r="V33" t="n">
-        <v>407.0699593151251</v>
+        <v>149.3438383838388</v>
       </c>
       <c r="W33" t="n">
-        <v>407.0699593151251</v>
+        <v>149.3438383838388</v>
       </c>
       <c r="X33" t="n">
-        <v>407.0699593151251</v>
+        <v>10.96</v>
       </c>
       <c r="Y33" t="n">
-        <v>407.0699593151251</v>
+        <v>10.96</v>
       </c>
     </row>
     <row r="34">
@@ -6825,76 +6825,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>94.29919447258872</v>
+        <v>36.72311713606749</v>
       </c>
       <c r="C34" t="n">
-        <v>21.8494503836547</v>
+        <v>36.72311713606749</v>
       </c>
       <c r="D34" t="n">
-        <v>21.8494503836547</v>
+        <v>36.72311713606749</v>
       </c>
       <c r="E34" t="n">
-        <v>21.8494503836547</v>
+        <v>36.72311713606749</v>
       </c>
       <c r="F34" t="n">
-        <v>21.8494503836547</v>
+        <v>36.72311713606749</v>
       </c>
       <c r="G34" t="n">
+        <v>36.72311713606749</v>
+      </c>
+      <c r="H34" t="n">
+        <v>15.26273143978108</v>
+      </c>
+      <c r="I34" t="n">
+        <v>61.23630611356892</v>
+      </c>
+      <c r="J34" t="n">
+        <v>181.1061177949651</v>
+      </c>
+      <c r="K34" t="n">
+        <v>181.1061177949651</v>
+      </c>
+      <c r="L34" t="n">
+        <v>181.1061177949651</v>
+      </c>
+      <c r="M34" t="n">
+        <v>181.1061177949651</v>
+      </c>
+      <c r="N34" t="n">
+        <v>181.1061177949651</v>
+      </c>
+      <c r="O34" t="n">
+        <v>181.1061177949651</v>
+      </c>
+      <c r="P34" t="n">
+        <v>181.1061177949651</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>155.291984714054</v>
+      </c>
+      <c r="R34" t="n">
+        <v>16.9081463302156</v>
+      </c>
+      <c r="S34" t="n">
+        <v>16.9081463302156</v>
+      </c>
+      <c r="T34" t="n">
         <v>10.96</v>
       </c>
-      <c r="H34" t="n">
-        <v>10.96</v>
-      </c>
-      <c r="I34" t="n">
-        <v>56.93357467378785</v>
-      </c>
-      <c r="J34" t="n">
-        <v>176.8033863551844</v>
-      </c>
-      <c r="K34" t="n">
-        <v>176.8033863551844</v>
-      </c>
-      <c r="L34" t="n">
-        <v>176.8033863551844</v>
-      </c>
-      <c r="M34" t="n">
-        <v>176.8033863551844</v>
-      </c>
-      <c r="N34" t="n">
-        <v>176.8033863551844</v>
-      </c>
-      <c r="O34" t="n">
-        <v>176.8033863551844</v>
-      </c>
-      <c r="P34" t="n">
-        <v>176.8033863551844</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>176.8033863551844</v>
-      </c>
-      <c r="R34" t="n">
-        <v>176.8033863551844</v>
-      </c>
-      <c r="S34" t="n">
-        <v>176.8033863551844</v>
-      </c>
-      <c r="T34" t="n">
-        <v>176.8033863551844</v>
-      </c>
       <c r="U34" t="n">
-        <v>226.3842114524874</v>
+        <v>60.54082509730302</v>
       </c>
       <c r="V34" t="n">
-        <v>228.1956043384334</v>
+        <v>62.35221798324899</v>
       </c>
       <c r="W34" t="n">
-        <v>228.1956043384334</v>
+        <v>36.72311713606749</v>
       </c>
       <c r="X34" t="n">
-        <v>181.2828311767086</v>
+        <v>36.72311713606749</v>
       </c>
       <c r="Y34" t="n">
-        <v>181.2828311767086</v>
+        <v>36.72311713606749</v>
       </c>
     </row>
     <row r="35">
@@ -6904,22 +6904,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>548</v>
+        <v>287.7276767676788</v>
       </c>
       <c r="C35" t="n">
-        <v>548</v>
+        <v>287.7276767676788</v>
       </c>
       <c r="D35" t="n">
-        <v>409.616161616161</v>
+        <v>287.7276767676788</v>
       </c>
       <c r="E35" t="n">
-        <v>271.2323232323221</v>
+        <v>149.3438383838396</v>
       </c>
       <c r="F35" t="n">
-        <v>271.2323232323221</v>
+        <v>149.3438383838396</v>
       </c>
       <c r="G35" t="n">
-        <v>132.8484848484828</v>
+        <v>149.3438383838396</v>
       </c>
       <c r="H35" t="n">
         <v>10.96</v>
@@ -6937,7 +6937,7 @@
         <v>385.0075447721345</v>
       </c>
       <c r="M35" t="n">
-        <v>272.9122181374765</v>
+        <v>328.4791837710628</v>
       </c>
       <c r="N35" t="n">
         <v>272.9122181374765</v>
@@ -6955,25 +6955,25 @@
         <v>548</v>
       </c>
       <c r="S35" t="n">
-        <v>548</v>
+        <v>409.6161616161602</v>
       </c>
       <c r="T35" t="n">
-        <v>548</v>
+        <v>287.7276767676788</v>
       </c>
       <c r="U35" t="n">
-        <v>548</v>
+        <v>287.7276767676788</v>
       </c>
       <c r="V35" t="n">
-        <v>548</v>
+        <v>287.7276767676788</v>
       </c>
       <c r="W35" t="n">
-        <v>548</v>
+        <v>287.7276767676788</v>
       </c>
       <c r="X35" t="n">
-        <v>548</v>
+        <v>287.7276767676788</v>
       </c>
       <c r="Y35" t="n">
-        <v>548</v>
+        <v>287.7276767676788</v>
       </c>
     </row>
     <row r="36">
@@ -6983,22 +6983,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>10.96</v>
+        <v>545.4537976989648</v>
       </c>
       <c r="C36" t="n">
-        <v>10.96</v>
+        <v>545.4537976989648</v>
       </c>
       <c r="D36" t="n">
-        <v>10.96</v>
+        <v>407.0699593151256</v>
       </c>
       <c r="E36" t="n">
-        <v>10.96</v>
+        <v>268.6861209312864</v>
       </c>
       <c r="F36" t="n">
-        <v>10.96</v>
+        <v>134.9127657876943</v>
       </c>
       <c r="G36" t="n">
-        <v>10.96</v>
+        <v>134.9127657876943</v>
       </c>
       <c r="H36" t="n">
         <v>10.96</v>
@@ -7007,52 +7007,52 @@
         <v>10.96</v>
       </c>
       <c r="J36" t="n">
-        <v>122.3987121337884</v>
+        <v>70.46613416810764</v>
       </c>
       <c r="K36" t="n">
-        <v>158.6198426983167</v>
+        <v>106.687264732636</v>
       </c>
       <c r="L36" t="n">
-        <v>233.941574877562</v>
+        <v>182.0089969118813</v>
       </c>
       <c r="M36" t="n">
-        <v>271.6310943946149</v>
+        <v>219.6985164289342</v>
       </c>
       <c r="N36" t="n">
-        <v>348.7558622912256</v>
+        <v>296.8232843255449</v>
       </c>
       <c r="O36" t="n">
-        <v>484.3858622912256</v>
+        <v>363.2158845359918</v>
       </c>
       <c r="P36" t="n">
-        <v>545.4537976989657</v>
+        <v>424.2838199437319</v>
       </c>
       <c r="Q36" t="n">
-        <v>545.4537976989657</v>
+        <v>545.4537976989648</v>
       </c>
       <c r="R36" t="n">
-        <v>545.4537976989657</v>
+        <v>545.4537976989648</v>
       </c>
       <c r="S36" t="n">
-        <v>545.4537976989657</v>
+        <v>545.4537976989648</v>
       </c>
       <c r="T36" t="n">
-        <v>407.0699593151264</v>
+        <v>545.4537976989648</v>
       </c>
       <c r="U36" t="n">
-        <v>268.686120931287</v>
+        <v>545.4537976989648</v>
       </c>
       <c r="V36" t="n">
-        <v>268.686120931287</v>
+        <v>545.4537976989648</v>
       </c>
       <c r="W36" t="n">
-        <v>268.686120931287</v>
+        <v>545.4537976989648</v>
       </c>
       <c r="X36" t="n">
-        <v>268.686120931287</v>
+        <v>545.4537976989648</v>
       </c>
       <c r="Y36" t="n">
-        <v>149.3438383838388</v>
+        <v>545.4537976989648</v>
       </c>
     </row>
     <row r="37">
@@ -7062,76 +7062,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>32.42038569628641</v>
+        <v>36.72311713606749</v>
       </c>
       <c r="C37" t="n">
-        <v>32.42038569628641</v>
+        <v>36.72311713606749</v>
       </c>
       <c r="D37" t="n">
-        <v>32.42038569628641</v>
+        <v>36.72311713606749</v>
       </c>
       <c r="E37" t="n">
-        <v>32.42038569628641</v>
+        <v>36.72311713606749</v>
       </c>
       <c r="F37" t="n">
-        <v>32.42038569628641</v>
+        <v>36.72311713606749</v>
       </c>
       <c r="G37" t="n">
-        <v>32.42038569628641</v>
+        <v>36.72311713606749</v>
       </c>
       <c r="H37" t="n">
+        <v>15.26273143978108</v>
+      </c>
+      <c r="I37" t="n">
+        <v>45.47611779496555</v>
+      </c>
+      <c r="J37" t="n">
+        <v>181.1061177949655</v>
+      </c>
+      <c r="K37" t="n">
+        <v>181.1061177949655</v>
+      </c>
+      <c r="L37" t="n">
+        <v>66.52874873345655</v>
+      </c>
+      <c r="M37" t="n">
+        <v>16.9081463302156</v>
+      </c>
+      <c r="N37" t="n">
+        <v>16.9081463302156</v>
+      </c>
+      <c r="O37" t="n">
+        <v>16.9081463302156</v>
+      </c>
+      <c r="P37" t="n">
+        <v>16.9081463302156</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>16.9081463302156</v>
+      </c>
+      <c r="R37" t="n">
+        <v>16.9081463302156</v>
+      </c>
+      <c r="S37" t="n">
+        <v>16.9081463302156</v>
+      </c>
+      <c r="T37" t="n">
         <v>10.96</v>
       </c>
-      <c r="I37" t="n">
-        <v>56.93357467378785</v>
-      </c>
-      <c r="J37" t="n">
-        <v>176.8033863551852</v>
-      </c>
-      <c r="K37" t="n">
-        <v>176.8033863551852</v>
-      </c>
-      <c r="L37" t="n">
-        <v>176.8033863551852</v>
-      </c>
-      <c r="M37" t="n">
-        <v>176.8033863551852</v>
-      </c>
-      <c r="N37" t="n">
-        <v>176.8033863551852</v>
-      </c>
-      <c r="O37" t="n">
-        <v>176.8033863551852</v>
-      </c>
-      <c r="P37" t="n">
-        <v>176.8033863551852</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>176.8033863551852</v>
-      </c>
-      <c r="R37" t="n">
-        <v>176.8033863551852</v>
-      </c>
-      <c r="S37" t="n">
-        <v>176.8033863551852</v>
-      </c>
-      <c r="T37" t="n">
-        <v>176.8033863551852</v>
-      </c>
       <c r="U37" t="n">
-        <v>226.3842114524882</v>
+        <v>60.54082509730302</v>
       </c>
       <c r="V37" t="n">
-        <v>228.1956043384341</v>
+        <v>62.35221798324899</v>
       </c>
       <c r="W37" t="n">
-        <v>202.5665034912526</v>
+        <v>36.72311713606749</v>
       </c>
       <c r="X37" t="n">
-        <v>202.5665034912526</v>
+        <v>36.72311713606749</v>
       </c>
       <c r="Y37" t="n">
-        <v>115.2277632392704</v>
+        <v>36.72311713606749</v>
       </c>
     </row>
     <row r="38">
@@ -7141,22 +7141,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>409.61616161616</v>
+        <v>10.96</v>
       </c>
       <c r="C38" t="n">
-        <v>287.727676767679</v>
+        <v>10.96</v>
       </c>
       <c r="D38" t="n">
-        <v>287.727676767679</v>
+        <v>10.96</v>
       </c>
       <c r="E38" t="n">
-        <v>149.3438383838399</v>
+        <v>10.96</v>
       </c>
       <c r="F38" t="n">
-        <v>149.3438383838399</v>
+        <v>10.96</v>
       </c>
       <c r="G38" t="n">
-        <v>149.3438383838399</v>
+        <v>10.96</v>
       </c>
       <c r="H38" t="n">
         <v>10.96</v>
@@ -7174,7 +7174,7 @@
         <v>385.0075447721345</v>
       </c>
       <c r="M38" t="n">
-        <v>272.9122181374765</v>
+        <v>328.4791837710628</v>
       </c>
       <c r="N38" t="n">
         <v>272.9122181374765</v>
@@ -7192,25 +7192,25 @@
         <v>548</v>
       </c>
       <c r="S38" t="n">
-        <v>409.61616161616</v>
+        <v>409.6161616161604</v>
       </c>
       <c r="T38" t="n">
-        <v>409.61616161616</v>
+        <v>271.2323232323208</v>
       </c>
       <c r="U38" t="n">
-        <v>409.61616161616</v>
+        <v>132.8484848484812</v>
       </c>
       <c r="V38" t="n">
-        <v>409.61616161616</v>
+        <v>10.96</v>
       </c>
       <c r="W38" t="n">
-        <v>409.61616161616</v>
+        <v>10.96</v>
       </c>
       <c r="X38" t="n">
-        <v>409.61616161616</v>
+        <v>10.96</v>
       </c>
       <c r="Y38" t="n">
-        <v>409.61616161616</v>
+        <v>10.96</v>
       </c>
     </row>
     <row r="39">
@@ -7220,22 +7220,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>130.3022825474469</v>
+        <v>10.96</v>
       </c>
       <c r="C39" t="n">
-        <v>130.3022825474469</v>
+        <v>10.96</v>
       </c>
       <c r="D39" t="n">
-        <v>130.3022825474469</v>
+        <v>10.96</v>
       </c>
       <c r="E39" t="n">
-        <v>130.3022825474469</v>
+        <v>10.96</v>
       </c>
       <c r="F39" t="n">
-        <v>130.3022825474469</v>
+        <v>10.96</v>
       </c>
       <c r="G39" t="n">
-        <v>130.3022825474469</v>
+        <v>10.96</v>
       </c>
       <c r="H39" t="n">
         <v>10.96</v>
@@ -7244,52 +7244,52 @@
         <v>10.96</v>
       </c>
       <c r="J39" t="n">
-        <v>146.59</v>
+        <v>70.46613416810764</v>
       </c>
       <c r="K39" t="n">
-        <v>182.8111305645284</v>
+        <v>106.687264732636</v>
       </c>
       <c r="L39" t="n">
-        <v>258.1328627437737</v>
+        <v>182.0089969118813</v>
       </c>
       <c r="M39" t="n">
-        <v>295.8223822608265</v>
+        <v>219.6985164289342</v>
       </c>
       <c r="N39" t="n">
-        <v>372.9471501574373</v>
+        <v>296.8232843255449</v>
       </c>
       <c r="O39" t="n">
-        <v>439.3397503678842</v>
+        <v>363.2158845359918</v>
       </c>
       <c r="P39" t="n">
-        <v>500.4076857756243</v>
+        <v>424.2838199437319</v>
       </c>
       <c r="Q39" t="n">
-        <v>545.453797698965</v>
+        <v>545.4537976989648</v>
       </c>
       <c r="R39" t="n">
-        <v>545.453797698965</v>
+        <v>545.4537976989648</v>
       </c>
       <c r="S39" t="n">
-        <v>545.453797698965</v>
+        <v>545.4537976989648</v>
       </c>
       <c r="T39" t="n">
-        <v>407.0699593151255</v>
+        <v>545.4537976989648</v>
       </c>
       <c r="U39" t="n">
-        <v>268.6861209312859</v>
+        <v>545.4537976989648</v>
       </c>
       <c r="V39" t="n">
-        <v>130.3022825474469</v>
+        <v>407.0699593151259</v>
       </c>
       <c r="W39" t="n">
-        <v>130.3022825474469</v>
+        <v>268.686120931287</v>
       </c>
       <c r="X39" t="n">
-        <v>130.3022825474469</v>
+        <v>149.3438383838389</v>
       </c>
       <c r="Y39" t="n">
-        <v>130.3022825474469</v>
+        <v>10.96</v>
       </c>
     </row>
     <row r="40">
@@ -7302,70 +7302,70 @@
         <v>104.8701297852204</v>
       </c>
       <c r="C40" t="n">
-        <v>32.4203856962864</v>
+        <v>32.42038569628641</v>
       </c>
       <c r="D40" t="n">
-        <v>32.4203856962864</v>
+        <v>32.42038569628641</v>
       </c>
       <c r="E40" t="n">
-        <v>32.4203856962864</v>
+        <v>32.42038569628641</v>
       </c>
       <c r="F40" t="n">
-        <v>32.4203856962864</v>
+        <v>32.42038569628641</v>
       </c>
       <c r="G40" t="n">
-        <v>32.4203856962864</v>
+        <v>32.42038569628641</v>
       </c>
       <c r="H40" t="n">
         <v>10.96</v>
       </c>
       <c r="I40" t="n">
-        <v>56.93357467378783</v>
+        <v>56.93357467378785</v>
       </c>
       <c r="J40" t="n">
-        <v>176.8033863551836</v>
+        <v>176.8033863551845</v>
       </c>
       <c r="K40" t="n">
-        <v>176.8033863551836</v>
+        <v>176.8033863551845</v>
       </c>
       <c r="L40" t="n">
-        <v>176.8033863551836</v>
+        <v>172.3938992313507</v>
       </c>
       <c r="M40" t="n">
-        <v>176.8033863551836</v>
+        <v>172.3938992313507</v>
       </c>
       <c r="N40" t="n">
-        <v>176.8033863551836</v>
+        <v>172.3938992313507</v>
       </c>
       <c r="O40" t="n">
-        <v>176.8033863551836</v>
+        <v>172.3938992313507</v>
       </c>
       <c r="P40" t="n">
-        <v>176.8033863551836</v>
+        <v>172.3938992313507</v>
       </c>
       <c r="Q40" t="n">
-        <v>176.8033863551836</v>
+        <v>172.3938992313507</v>
       </c>
       <c r="R40" t="n">
-        <v>176.8033863551836</v>
+        <v>172.3938992313507</v>
       </c>
       <c r="S40" t="n">
-        <v>85.05515897936853</v>
+        <v>172.3938992313507</v>
       </c>
       <c r="T40" t="n">
-        <v>79.10701264915292</v>
+        <v>166.4457529011351</v>
       </c>
       <c r="U40" t="n">
-        <v>128.687837746456</v>
+        <v>216.0265779984381</v>
       </c>
       <c r="V40" t="n">
-        <v>130.4992306324019</v>
+        <v>217.8379708843841</v>
       </c>
       <c r="W40" t="n">
-        <v>104.8701297852204</v>
+        <v>192.2088700372026</v>
       </c>
       <c r="X40" t="n">
-        <v>104.8701297852204</v>
+        <v>192.2088700372026</v>
       </c>
       <c r="Y40" t="n">
         <v>104.8701297852204</v>
@@ -7378,25 +7378,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>312.6259707927874</v>
+        <v>10.96</v>
       </c>
       <c r="C41" t="n">
-        <v>312.6259707927874</v>
+        <v>10.96</v>
       </c>
       <c r="D41" t="n">
-        <v>312.6259707927874</v>
+        <v>10.96</v>
       </c>
       <c r="E41" t="n">
-        <v>312.6259707927874</v>
+        <v>10.96</v>
       </c>
       <c r="F41" t="n">
-        <v>312.6259707927874</v>
+        <v>10.96</v>
       </c>
       <c r="G41" t="n">
-        <v>174.2421324089476</v>
+        <v>10.96</v>
       </c>
       <c r="H41" t="n">
-        <v>35.85829402510789</v>
+        <v>10.96</v>
       </c>
       <c r="I41" t="n">
         <v>10.96</v>
@@ -7411,7 +7411,7 @@
         <v>385.0075447721345</v>
       </c>
       <c r="M41" t="n">
-        <v>310.2973655892446</v>
+        <v>275.2365704845514</v>
       </c>
       <c r="N41" t="n">
         <v>272.9122181374765</v>
@@ -7435,19 +7435,19 @@
         <v>548</v>
       </c>
       <c r="U41" t="n">
-        <v>451.0098091766264</v>
+        <v>409.6161616161604</v>
       </c>
       <c r="V41" t="n">
-        <v>312.6259707927874</v>
+        <v>287.7276767676778</v>
       </c>
       <c r="W41" t="n">
-        <v>312.6259707927874</v>
+        <v>149.343838383839</v>
       </c>
       <c r="X41" t="n">
-        <v>312.6259707927874</v>
+        <v>10.96</v>
       </c>
       <c r="Y41" t="n">
-        <v>312.6259707927874</v>
+        <v>10.96</v>
       </c>
     </row>
     <row r="42">
@@ -7457,76 +7457,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>149.3438383838391</v>
+        <v>309.6599293414447</v>
       </c>
       <c r="C42" t="n">
-        <v>10.96</v>
+        <v>309.6599293414447</v>
       </c>
       <c r="D42" t="n">
-        <v>10.96</v>
+        <v>309.6599293414447</v>
       </c>
       <c r="E42" t="n">
-        <v>10.96</v>
+        <v>309.6599293414447</v>
       </c>
       <c r="F42" t="n">
-        <v>10.96</v>
+        <v>171.2760909576057</v>
       </c>
       <c r="G42" t="n">
-        <v>10.96</v>
+        <v>32.89225257376621</v>
       </c>
       <c r="H42" t="n">
-        <v>10.96</v>
+        <v>32.89225257376621</v>
       </c>
       <c r="I42" t="n">
         <v>10.96</v>
       </c>
       <c r="J42" t="n">
-        <v>10.96</v>
+        <v>97.78724867378017</v>
       </c>
       <c r="K42" t="n">
-        <v>47.18113056452834</v>
+        <v>134.0083792383085</v>
       </c>
       <c r="L42" t="n">
-        <v>182.8111305645283</v>
+        <v>209.3301114175538</v>
       </c>
       <c r="M42" t="n">
-        <v>182.8111305645283</v>
+        <v>209.3301114175538</v>
       </c>
       <c r="N42" t="n">
-        <v>182.8111305645283</v>
+        <v>209.3301114175538</v>
       </c>
       <c r="O42" t="n">
-        <v>249.2037307749752</v>
+        <v>275.7227116280007</v>
       </c>
       <c r="P42" t="n">
-        <v>344.4197586780546</v>
+        <v>336.7906470357408</v>
       </c>
       <c r="Q42" t="n">
-        <v>447.7697364332874</v>
+        <v>440.1406247909736</v>
       </c>
       <c r="R42" t="n">
-        <v>426.1115151515173</v>
+        <v>440.1406247909736</v>
       </c>
       <c r="S42" t="n">
-        <v>426.1115151515173</v>
+        <v>440.1406247909736</v>
       </c>
       <c r="T42" t="n">
-        <v>426.1115151515173</v>
+        <v>440.1406247909736</v>
       </c>
       <c r="U42" t="n">
-        <v>426.1115151515173</v>
+        <v>309.6599293414447</v>
       </c>
       <c r="V42" t="n">
-        <v>287.7276767676783</v>
+        <v>309.6599293414447</v>
       </c>
       <c r="W42" t="n">
-        <v>287.7276767676783</v>
+        <v>309.6599293414447</v>
       </c>
       <c r="X42" t="n">
-        <v>287.7276767676783</v>
+        <v>309.6599293414447</v>
       </c>
       <c r="Y42" t="n">
-        <v>287.7276767676783</v>
+        <v>309.6599293414447</v>
       </c>
     </row>
     <row r="43">
@@ -7560,43 +7560,43 @@
         <v>16.99073317802753</v>
       </c>
       <c r="J43" t="n">
-        <v>81.75643298932569</v>
+        <v>63.47370512677711</v>
       </c>
       <c r="K43" t="n">
-        <v>81.75643298932569</v>
+        <v>63.47370512677711</v>
       </c>
       <c r="L43" t="n">
-        <v>81.75643298932569</v>
+        <v>63.47370512677711</v>
       </c>
       <c r="M43" t="n">
-        <v>81.75643298932569</v>
+        <v>63.47370512677711</v>
       </c>
       <c r="N43" t="n">
-        <v>81.75643298932569</v>
+        <v>63.47370512677711</v>
       </c>
       <c r="O43" t="n">
-        <v>81.75643298932569</v>
+        <v>63.47370512677711</v>
       </c>
       <c r="P43" t="n">
-        <v>81.75643298932569</v>
+        <v>63.47370512677711</v>
       </c>
       <c r="Q43" t="n">
-        <v>10.96</v>
+        <v>63.47370512677711</v>
       </c>
       <c r="R43" t="n">
-        <v>10.96</v>
+        <v>63.47370512677711</v>
       </c>
       <c r="S43" t="n">
-        <v>10.96</v>
+        <v>63.47370512677711</v>
       </c>
       <c r="T43" t="n">
-        <v>10.96</v>
+        <v>39.34374061474331</v>
       </c>
       <c r="U43" t="n">
-        <v>10.96</v>
+        <v>71.10456571204635</v>
       </c>
       <c r="V43" t="n">
-        <v>10.96</v>
+        <v>54.77091902899969</v>
       </c>
       <c r="W43" t="n">
         <v>10.96</v>
@@ -7615,19 +7615,19 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>10.96</v>
+        <v>287.7276767676776</v>
       </c>
       <c r="C44" t="n">
-        <v>10.96</v>
+        <v>149.3438383838389</v>
       </c>
       <c r="D44" t="n">
-        <v>10.96</v>
+        <v>149.3438383838389</v>
       </c>
       <c r="E44" t="n">
-        <v>10.96</v>
+        <v>149.3438383838389</v>
       </c>
       <c r="F44" t="n">
-        <v>10.96</v>
+        <v>149.3438383838389</v>
       </c>
       <c r="G44" t="n">
         <v>10.96</v>
@@ -7648,43 +7648,43 @@
         <v>385.0075447721345</v>
       </c>
       <c r="M44" t="n">
+        <v>385.0075447721345</v>
+      </c>
+      <c r="N44" t="n">
         <v>246.6237063882949</v>
       </c>
-      <c r="N44" t="n">
-        <v>108.239868004455</v>
-      </c>
       <c r="O44" t="n">
-        <v>243.8698680044552</v>
+        <v>382.2537063882949</v>
       </c>
       <c r="P44" t="n">
-        <v>379.4998680044553</v>
+        <v>517.883706388295</v>
       </c>
       <c r="Q44" t="n">
-        <v>383.3276498669784</v>
+        <v>521.7114882508181</v>
       </c>
       <c r="R44" t="n">
-        <v>244.9438114831391</v>
+        <v>521.7114882508181</v>
       </c>
       <c r="S44" t="n">
-        <v>106.5599730992999</v>
+        <v>521.7114882508181</v>
       </c>
       <c r="T44" t="n">
-        <v>106.5599730992999</v>
+        <v>426.1115151515162</v>
       </c>
       <c r="U44" t="n">
-        <v>106.5599730992999</v>
+        <v>426.1115151515162</v>
       </c>
       <c r="V44" t="n">
-        <v>106.5599730992999</v>
+        <v>426.1115151515162</v>
       </c>
       <c r="W44" t="n">
-        <v>106.5599730992999</v>
+        <v>426.1115151515162</v>
       </c>
       <c r="X44" t="n">
-        <v>10.96</v>
+        <v>426.1115151515162</v>
       </c>
       <c r="Y44" t="n">
-        <v>10.96</v>
+        <v>426.1115151515162</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>249.9633983619606</v>
+        <v>41.48079221903999</v>
       </c>
       <c r="C45" t="n">
-        <v>249.9633983619606</v>
+        <v>41.48079221903999</v>
       </c>
       <c r="D45" t="n">
-        <v>249.9633983619606</v>
+        <v>41.48079221903999</v>
       </c>
       <c r="E45" t="n">
-        <v>249.9633983619606</v>
+        <v>41.48079221903999</v>
       </c>
       <c r="F45" t="n">
-        <v>249.9633983619606</v>
+        <v>41.48079221903999</v>
       </c>
       <c r="G45" t="n">
-        <v>111.5795599781216</v>
+        <v>41.48079221903999</v>
       </c>
       <c r="H45" t="n">
-        <v>111.5795599781216</v>
+        <v>41.48079221903999</v>
       </c>
       <c r="I45" t="n">
-        <v>29.69416602965453</v>
+        <v>41.48079221903999</v>
       </c>
       <c r="J45" t="n">
+        <v>22.74662618938547</v>
+      </c>
+      <c r="K45" t="n">
+        <v>58.9677567539138</v>
+      </c>
+      <c r="L45" t="n">
+        <v>134.2894889331591</v>
+      </c>
+      <c r="M45" t="n">
+        <v>134.2894889331591</v>
+      </c>
+      <c r="N45" t="n">
         <v>10.96</v>
       </c>
-      <c r="K45" t="n">
-        <v>47.18113056452834</v>
-      </c>
-      <c r="L45" t="n">
-        <v>122.5028627437736</v>
-      </c>
-      <c r="M45" t="n">
-        <v>122.5028627437736</v>
-      </c>
-      <c r="N45" t="n">
-        <v>122.5028627437736</v>
-      </c>
       <c r="O45" t="n">
-        <v>188.8954629542205</v>
+        <v>77.35260021044687</v>
       </c>
       <c r="P45" t="n">
-        <v>249.9633983619606</v>
+        <v>138.4205356181869</v>
       </c>
       <c r="Q45" t="n">
-        <v>249.9633983619606</v>
+        <v>138.4205356181869</v>
       </c>
       <c r="R45" t="n">
-        <v>249.9633983619606</v>
+        <v>41.48079221903999</v>
       </c>
       <c r="S45" t="n">
-        <v>249.9633983619606</v>
+        <v>41.48079221903999</v>
       </c>
       <c r="T45" t="n">
-        <v>249.9633983619606</v>
+        <v>41.48079221903999</v>
       </c>
       <c r="U45" t="n">
-        <v>249.9633983619606</v>
+        <v>41.48079221903999</v>
       </c>
       <c r="V45" t="n">
-        <v>249.9633983619606</v>
+        <v>41.48079221903999</v>
       </c>
       <c r="W45" t="n">
-        <v>249.9633983619606</v>
+        <v>41.48079221903999</v>
       </c>
       <c r="X45" t="n">
-        <v>249.9633983619606</v>
+        <v>41.48079221903999</v>
       </c>
       <c r="Y45" t="n">
-        <v>249.9633983619606</v>
+        <v>41.48079221903999</v>
       </c>
     </row>
     <row r="46">
@@ -8043,25 +8043,25 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J3" t="n">
-        <v>227.4647419277884</v>
+        <v>19.54682436935798</v>
       </c>
       <c r="K3" t="n">
-        <v>78.23279137943454</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>45.77225964220156</v>
       </c>
       <c r="M3" t="n">
         <v>397.9297782656032</v>
       </c>
       <c r="N3" t="n">
-        <v>123.0961940438275</v>
+        <v>358.0961940438275</v>
       </c>
       <c r="O3" t="n">
-        <v>167.936767464195</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>173.3152167598585</v>
       </c>
       <c r="Q3" t="n">
         <v>17.27519534353338</v>
@@ -8289,16 +8289,16 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>397.9297782656032</v>
+        <v>302.8473528851792</v>
       </c>
       <c r="N6" t="n">
-        <v>358.0961940438275</v>
+        <v>123.0961940438275</v>
       </c>
       <c r="O6" t="n">
-        <v>11.16955884362957</v>
+        <v>167.936767464195</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>173.3152167598585</v>
       </c>
       <c r="Q6" t="n">
         <v>17.27519534353338</v>
@@ -8520,22 +8520,22 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K9" t="n">
-        <v>198.4129994297693</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>397.9297782656032</v>
+        <v>162.9297782656032</v>
       </c>
       <c r="N9" t="n">
-        <v>123.0961940438275</v>
+        <v>263.0137686634035</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>167.936767464195</v>
       </c>
       <c r="P9" t="n">
-        <v>47.75655941386024</v>
+        <v>173.3152167598585</v>
       </c>
       <c r="Q9" t="n">
         <v>17.27519534353338</v>
@@ -8936,7 +8936,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>213.6409664189359</v>
+        <v>294.54111633436</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -8997,7 +8997,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>158.9174422431866</v>
+        <v>44.29768863413632</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -9006,7 +9006,7 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>37.25882972273579</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -9173,7 +9173,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>212.6409664189359</v>
+        <v>241.7435683929509</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -9225,7 +9225,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>17.72758189252907</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -9237,7 +9237,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>214.3050483711875</v>
+        <v>118.0887739772001</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -9249,7 +9249,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>17.27519534353338</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -9307,7 +9307,7 @@
         <v>22.34630454117203</v>
       </c>
       <c r="J19" t="n">
-        <v>122.5801012007089</v>
+        <v>134.2003162992274</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -9544,7 +9544,7 @@
         <v>22.34630454117203</v>
       </c>
       <c r="J22" t="n">
-        <v>101.0397511726042</v>
+        <v>101.0397511726036</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -9632,7 +9632,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>40.81966447069595</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -9647,7 +9647,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>212.6409664189359</v>
+        <v>294.54111633436</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -9714,10 +9714,10 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>53.97162630439051</v>
       </c>
       <c r="O24" t="n">
-        <v>140.8469123022666</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -9781,7 +9781,7 @@
         <v>22.34630454117203</v>
       </c>
       <c r="J25" t="n">
-        <v>116.9709210946626</v>
+        <v>134.2003162992274</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -10255,7 +10255,7 @@
         <v>22.34630454117203</v>
       </c>
       <c r="J31" t="n">
-        <v>37.6607190607043</v>
+        <v>37.66071906070395</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -10492,7 +10492,7 @@
         <v>22.34630454117203</v>
       </c>
       <c r="J34" t="n">
-        <v>37.66071906070543</v>
+        <v>37.66071906070508</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -10726,10 +10726,10 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>22.34630454117203</v>
+        <v>6.426922401168624</v>
       </c>
       <c r="J37" t="n">
-        <v>37.66071906070621</v>
+        <v>53.58010120070895</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -10884,7 +10884,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>3.712930048028547</v>
+        <v>3.712930048028539</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -10966,7 +10966,7 @@
         <v>22.34630454117203</v>
       </c>
       <c r="J40" t="n">
-        <v>37.66071906070465</v>
+        <v>37.66071906070552</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -12294,25 +12294,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-481.9993129555745</v>
+        <v>-331.6990979018111</v>
       </c>
       <c r="C11" t="n">
-        <v>-449.4745782429939</v>
+        <v>-316.0362986731014</v>
       </c>
       <c r="D11" t="n">
-        <v>-410.3391557398498</v>
+        <v>-280.7189406860864</v>
       </c>
       <c r="E11" t="n">
-        <v>-404.3632896068686</v>
+        <v>-277.9886659509547</v>
       </c>
       <c r="F11" t="n">
-        <v>-404.8896287080119</v>
+        <v>-276.3623168800549</v>
       </c>
       <c r="G11" t="n">
-        <v>-403.7573722870162</v>
+        <v>-280.5454373434814</v>
       </c>
       <c r="H11" t="n">
-        <v>-408.0096587035274</v>
+        <v>-343.5735880275669</v>
       </c>
       <c r="I11" t="n">
         <v>-270.7281754064649</v>
@@ -12345,25 +12345,25 @@
         <v>-545.4197151626545</v>
       </c>
       <c r="S11" t="n">
-        <v>-494.8481678023229</v>
+        <v>-493.7750927496402</v>
       </c>
       <c r="T11" t="n">
-        <v>-586.6755817285639</v>
+        <v>-439.6704096315195</v>
       </c>
       <c r="U11" t="n">
-        <v>-649.2212965486107</v>
+        <v>-448.6221654090418</v>
       </c>
       <c r="V11" t="n">
-        <v>-629.8510241668239</v>
+        <v>-418.6557553496196</v>
       </c>
       <c r="W11" t="n">
-        <v>-638.3734759809475</v>
+        <v>-434.175626518582</v>
       </c>
       <c r="X11" t="n">
-        <v>-592.2818334606677</v>
+        <v>-410.5760270090548</v>
       </c>
       <c r="Y11" t="n">
-        <v>-511.3174326828064</v>
+        <v>-335.1802283817312</v>
       </c>
     </row>
     <row r="12">
@@ -12373,25 +12373,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-384.5565566463266</v>
+        <v>-287.7951208435828</v>
       </c>
       <c r="C12" t="n">
-        <v>-361.0999124455193</v>
+        <v>-272.1075174881593</v>
       </c>
       <c r="D12" t="n">
-        <v>-347.9376868977026</v>
+        <v>-260.3897954627749</v>
       </c>
       <c r="E12" t="n">
-        <v>-342.6720972219126</v>
+        <v>-257.1409658537258</v>
       </c>
       <c r="F12" t="n">
-        <v>-339.6362423378769</v>
+        <v>-252.6333737802202</v>
       </c>
       <c r="G12" t="n">
-        <v>-325.7395358750273</v>
+        <v>-241.6866437866832</v>
       </c>
       <c r="H12" t="n">
-        <v>-332.1680871864211</v>
+        <v>-279.997980787977</v>
       </c>
       <c r="I12" t="n">
         <v>-234.8539677838776</v>
@@ -12421,28 +12421,28 @@
         <v>-190.354460434013</v>
       </c>
       <c r="R12" t="n">
-        <v>-547.2737972923793</v>
+        <v>-380.5048676619724</v>
       </c>
       <c r="S12" t="n">
-        <v>-466.5639999646113</v>
+        <v>-335.4715515361105</v>
       </c>
       <c r="T12" t="n">
-        <v>-405.3577652175138</v>
+        <v>-276.5060826044077</v>
       </c>
       <c r="U12" t="n">
-        <v>-400.2103597601867</v>
+        <v>-254.3060809410213</v>
       </c>
       <c r="V12" t="n">
-        <v>-414.5106671915202</v>
+        <v>-267.6494502273624</v>
       </c>
       <c r="W12" t="n">
-        <v>-432.3731429098285</v>
+        <v>-288.6712367342013</v>
       </c>
       <c r="X12" t="n">
-        <v>-419.8627394453875</v>
+        <v>-287.4440873306922</v>
       </c>
       <c r="Y12" t="n">
-        <v>-399.3913927661343</v>
+        <v>-269.9483329489301</v>
       </c>
     </row>
     <row r="13">
@@ -12452,25 +12452,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-287.1138003370787</v>
+        <v>-243.8911437853545</v>
       </c>
       <c r="C13" t="n">
-        <v>-272.7252466480447</v>
+        <v>-228.1787363032171</v>
       </c>
       <c r="D13" t="n">
-        <v>-285.5362180555555</v>
+        <v>-240.0606502394635</v>
       </c>
       <c r="E13" t="n">
-        <v>-280.9809048369565</v>
+        <v>-236.2932657564968</v>
       </c>
       <c r="F13" t="n">
-        <v>-274.3828559677419</v>
+        <v>-228.9044306803856</v>
       </c>
       <c r="G13" t="n">
-        <v>-245.04387284153</v>
+        <v>-202.827850229885</v>
       </c>
       <c r="H13" t="n">
-        <v>-228.7711261016186</v>
+        <v>-216.4223735483871</v>
       </c>
       <c r="I13" t="n">
         <v>-198.9797601612903</v>
@@ -12479,49 +12479,49 @@
         <v>-169.4692651351351</v>
       </c>
       <c r="K13" t="n">
-        <v>-288.520773801143</v>
+        <v>-209.5527724444444</v>
       </c>
       <c r="L13" t="n">
-        <v>-423.5476281577792</v>
+        <v>-227.9959222222222</v>
       </c>
       <c r="M13" t="n">
-        <v>-520.6316114025499</v>
+        <v>-225.2274288888889</v>
       </c>
       <c r="N13" t="n">
-        <v>-571.1850752716849</v>
+        <v>-224.3149960555556</v>
       </c>
       <c r="O13" t="n">
-        <v>-640.445564079015</v>
+        <v>-212.2016842222222</v>
       </c>
       <c r="P13" t="n">
-        <v>-687.4478973282775</v>
+        <v>-210.6823546111111</v>
       </c>
       <c r="Q13" t="n">
-        <v>-725.839266425598</v>
+        <v>-207.8862365405406</v>
       </c>
       <c r="R13" t="n">
-        <v>-726.6021279811511</v>
+        <v>-215.5900201612903</v>
       </c>
       <c r="S13" t="n">
-        <v>-362.3734797028554</v>
+        <v>-177.1680103225807</v>
       </c>
       <c r="T13" t="n">
-        <v>-210.0245665062577</v>
+        <v>-113.341755577296</v>
       </c>
       <c r="U13" t="n">
-        <v>-150.9583912744579</v>
+        <v>-59.98999647300078</v>
       </c>
       <c r="V13" t="n">
-        <v>-199.1703102162162</v>
+        <v>-116.6431451051051</v>
       </c>
       <c r="W13" t="n">
-        <v>-226.3728098387097</v>
+        <v>-143.1668469498208</v>
       </c>
       <c r="X13" t="n">
-        <v>-247.4436454301076</v>
+        <v>-164.3121476523298</v>
       </c>
       <c r="Y13" t="n">
-        <v>-287.4653528494624</v>
+        <v>-204.716437516129</v>
       </c>
     </row>
     <row r="14">
@@ -15937,76 +15937,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-481.9993129555745</v>
+        <v>-331.6990979018111</v>
       </c>
       <c r="C11" t="n">
-        <v>-449.4745782429939</v>
+        <v>-316.0362986731014</v>
       </c>
       <c r="D11" t="n">
-        <v>-410.3391557398498</v>
+        <v>-280.7189406860864</v>
       </c>
       <c r="E11" t="n">
-        <v>-404.3632896068686</v>
+        <v>-277.9886659509547</v>
       </c>
       <c r="F11" t="n">
-        <v>-404.8896287080119</v>
+        <v>-276.3623168800549</v>
       </c>
       <c r="G11" t="n">
-        <v>-403.7573722870162</v>
+        <v>-280.5454373434814</v>
       </c>
       <c r="H11" t="n">
-        <v>-408.0096587035274</v>
+        <v>-343.5735880275669</v>
       </c>
       <c r="I11" t="n">
-        <v>-150.0811596826846</v>
+        <v>-270.7281754064649</v>
       </c>
       <c r="J11" t="n">
-        <v>395.2617303410664</v>
+        <v>-35.04300624509033</v>
       </c>
       <c r="K11" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>916.1914086561842</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>516.0089179080152</v>
+        <v>-544.2621276423173</v>
       </c>
       <c r="N11" t="n">
-        <v>619.4144644189528</v>
+        <v>-477.2489580698352</v>
       </c>
       <c r="O11" t="n">
-        <v>962.6692363858147</v>
+        <v>-70.24786957409245</v>
       </c>
       <c r="P11" t="n">
-        <v>870.2908726334418</v>
+        <v>-0.2870600406814136</v>
       </c>
       <c r="Q11" t="n">
-        <v>443.0293889420883</v>
+        <v>-172.8226843274854</v>
       </c>
       <c r="R11" t="n">
-        <v>-250.8785988282945</v>
+        <v>-545.4197151626545</v>
       </c>
       <c r="S11" t="n">
-        <v>-494.8481678023229</v>
+        <v>-493.7750927496402</v>
       </c>
       <c r="T11" t="n">
-        <v>-586.6755817285639</v>
+        <v>-439.6704096315195</v>
       </c>
       <c r="U11" t="n">
-        <v>-649.2212965486107</v>
+        <v>-448.6221654090418</v>
       </c>
       <c r="V11" t="n">
-        <v>-629.8510241668239</v>
+        <v>-418.6557553496196</v>
       </c>
       <c r="W11" t="n">
-        <v>-638.3734759809475</v>
+        <v>-434.175626518582</v>
       </c>
       <c r="X11" t="n">
-        <v>-592.2818334606677</v>
+        <v>-410.5760270090548</v>
       </c>
       <c r="Y11" t="n">
-        <v>-511.3174326828064</v>
+        <v>-335.1802283817312</v>
       </c>
     </row>
     <row r="12">
@@ -16016,76 +16016,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-384.5565566463266</v>
+        <v>-287.7951208435828</v>
       </c>
       <c r="C12" t="n">
-        <v>-361.0999124455193</v>
+        <v>-272.1075174881593</v>
       </c>
       <c r="D12" t="n">
-        <v>-347.9376868977026</v>
+        <v>-260.3897954627749</v>
       </c>
       <c r="E12" t="n">
-        <v>-342.6720972219126</v>
+        <v>-257.1409658537258</v>
       </c>
       <c r="F12" t="n">
-        <v>-339.6362423378769</v>
+        <v>-252.6333737802202</v>
       </c>
       <c r="G12" t="n">
-        <v>-325.7395358750273</v>
+        <v>-241.6866437866832</v>
       </c>
       <c r="H12" t="n">
-        <v>-332.1680871864211</v>
+        <v>-279.997980787977</v>
       </c>
       <c r="I12" t="n">
-        <v>-217.1263858913485</v>
+        <v>-234.8539677838776</v>
       </c>
       <c r="J12" t="n">
-        <v>125.2086062376757</v>
+        <v>-102.2561356901127</v>
       </c>
       <c r="K12" t="n">
-        <v>191.1038546407913</v>
+        <v>-104.7763862222222</v>
       </c>
       <c r="L12" t="n">
-        <v>274.091375348687</v>
+        <v>-113.9979611111111</v>
       </c>
       <c r="M12" t="n">
-        <v>86.95004216450428</v>
+        <v>-384.7447782656031</v>
       </c>
       <c r="N12" t="n">
-        <v>134.6265501086548</v>
+        <v>-350.7819770626954</v>
       </c>
       <c r="O12" t="n">
-        <v>241.4570219027464</v>
+        <v>-141.2247768981573</v>
       </c>
       <c r="P12" t="n">
-        <v>113.6660045146532</v>
+        <v>-105.4847073258963</v>
       </c>
       <c r="Q12" t="n">
-        <v>-173.0792650904796</v>
+        <v>-190.354460434013</v>
       </c>
       <c r="R12" t="n">
-        <v>-547.2737972923793</v>
+        <v>-380.5048676619724</v>
       </c>
       <c r="S12" t="n">
-        <v>-466.5639999646113</v>
+        <v>-335.4715515361105</v>
       </c>
       <c r="T12" t="n">
-        <v>-405.3577652175138</v>
+        <v>-276.5060826044077</v>
       </c>
       <c r="U12" t="n">
-        <v>-400.2103597601867</v>
+        <v>-254.3060809410213</v>
       </c>
       <c r="V12" t="n">
-        <v>-414.5106671915202</v>
+        <v>-267.6494502273624</v>
       </c>
       <c r="W12" t="n">
-        <v>-432.3731429098285</v>
+        <v>-288.6712367342013</v>
       </c>
       <c r="X12" t="n">
-        <v>-419.8627394453875</v>
+        <v>-287.4440873306922</v>
       </c>
       <c r="Y12" t="n">
-        <v>-399.3913927661343</v>
+        <v>-269.9483329489301</v>
       </c>
     </row>
     <row r="13">
@@ -16095,76 +16095,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-287.1138003370787</v>
+        <v>-243.8911437853545</v>
       </c>
       <c r="C13" t="n">
-        <v>-272.7252466480447</v>
+        <v>-228.1787363032171</v>
       </c>
       <c r="D13" t="n">
-        <v>-285.5362180555555</v>
+        <v>-240.0606502394635</v>
       </c>
       <c r="E13" t="n">
-        <v>-280.9809048369565</v>
+        <v>-236.2932657564968</v>
       </c>
       <c r="F13" t="n">
-        <v>-274.3828559677419</v>
+        <v>-228.9044306803856</v>
       </c>
       <c r="G13" t="n">
-        <v>-245.04387284153</v>
+        <v>-202.827850229885</v>
       </c>
       <c r="H13" t="n">
-        <v>-228.7711261016186</v>
+        <v>-216.4223735483871</v>
       </c>
       <c r="I13" t="n">
-        <v>-176.6334556201183</v>
+        <v>-198.9797601612903</v>
       </c>
       <c r="J13" t="n">
-        <v>-35.26894883590776</v>
+        <v>-169.4692651351351</v>
       </c>
       <c r="K13" t="n">
-        <v>-288.520773801143</v>
+        <v>-209.5527724444444</v>
       </c>
       <c r="L13" t="n">
-        <v>-423.5476281577792</v>
+        <v>-227.9959222222222</v>
       </c>
       <c r="M13" t="n">
-        <v>-520.6316114025499</v>
+        <v>-225.2274288888889</v>
       </c>
       <c r="N13" t="n">
-        <v>-571.1850752716849</v>
+        <v>-224.3149960555556</v>
       </c>
       <c r="O13" t="n">
-        <v>-640.445564079015</v>
+        <v>-212.2016842222222</v>
       </c>
       <c r="P13" t="n">
-        <v>-687.4478973282775</v>
+        <v>-210.6823546111111</v>
       </c>
       <c r="Q13" t="n">
-        <v>-725.839266425598</v>
+        <v>-207.8862365405406</v>
       </c>
       <c r="R13" t="n">
-        <v>-726.6021279811511</v>
+        <v>-215.5900201612903</v>
       </c>
       <c r="S13" t="n">
-        <v>-362.3734797028554</v>
+        <v>-177.1680103225807</v>
       </c>
       <c r="T13" t="n">
-        <v>-210.0245665062577</v>
+        <v>-113.341755577296</v>
       </c>
       <c r="U13" t="n">
-        <v>-150.9583912744579</v>
+        <v>-59.98999647300078</v>
       </c>
       <c r="V13" t="n">
-        <v>-199.1703102162162</v>
+        <v>-116.6431451051051</v>
       </c>
       <c r="W13" t="n">
-        <v>-226.3728098387097</v>
+        <v>-143.1668469498208</v>
       </c>
       <c r="X13" t="n">
-        <v>-247.4436454301076</v>
+        <v>-164.3121476523298</v>
       </c>
       <c r="Y13" t="n">
-        <v>-287.4653528494624</v>
+        <v>-204.716437516129</v>
       </c>
     </row>
     <row r="14">
@@ -19601,34 +19601,34 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>120.6470157237802</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>916.1914086561842</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1060.271045550332</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1096.663422488788</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1032.917105959907</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>870.5779326741233</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>615.8520732695737</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>294.54111633436</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -19680,31 +19680,31 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>17.72758189252907</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>227.4647419277884</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>295.8802408630135</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>388.0893364597981</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>471.6948204301074</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>485.4085271713503</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>382.6817988009037</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>219.1507118405495</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>17.27519534353338</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -19759,10 +19759,10 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>22.34630454117203</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>134.2003162992274</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -22512,22 +22512,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>49.47457824299391</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>10.33915573984979</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>4.363289606868648</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2.121191382493578</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -22566,19 +22566,19 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>179.5131998190161</v>
+        <v>93.53918556982801</v>
       </c>
       <c r="U2" t="n">
-        <v>14.09040207624884</v>
+        <v>249.0904020762489</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>199.9386552229563</v>
+        <v>3.373475980947546</v>
       </c>
       <c r="X2" t="n">
-        <v>192.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -22706,10 +22706,10 @@
         <v>5.584054025500734</v>
       </c>
       <c r="N4" t="n">
-        <v>58.8730916651275</v>
+        <v>42.58361884706957</v>
       </c>
       <c r="O4" t="n">
-        <v>120.4177961789898</v>
+        <v>136.7072689970478</v>
       </c>
       <c r="P4" t="n">
         <v>198.6818645413923</v>
@@ -22718,7 +22718,7 @@
         <v>264.382266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>293.6017673254133</v>
+        <v>580.937437207049</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -22752,10 +22752,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>49.47457824299391</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>10.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -22800,25 +22800,25 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>57.56369544051385</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>179.5131998190161</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>80.59786226618365</v>
+        <v>23.9549000245398</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>229.8510241668239</v>
       </c>
       <c r="W5" t="n">
-        <v>3.373475980947546</v>
+        <v>238.3734759809475</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>111.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -22834,7 +22834,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>162.6428320084747</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -22943,7 +22943,7 @@
         <v>5.58405402550072</v>
       </c>
       <c r="N7" t="n">
-        <v>42.58361884706954</v>
+        <v>58.87309166512748</v>
       </c>
       <c r="O7" t="n">
         <v>136.7072689970477</v>
@@ -22952,10 +22952,10 @@
         <v>198.6818645413923</v>
       </c>
       <c r="Q7" t="n">
-        <v>264.382266425598</v>
+        <v>248.0927936075401</v>
       </c>
       <c r="R7" t="n">
-        <v>580.9374372070499</v>
+        <v>293.6017673254133</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -22986,7 +22986,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -23001,7 +23001,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.121191382493598</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -23037,10 +23037,10 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>57.56369544051385</v>
+        <v>144.1975657565853</v>
       </c>
       <c r="T8" t="n">
-        <v>179.5131998190161</v>
+        <v>112.3123096427081</v>
       </c>
       <c r="U8" t="n">
         <v>14.09040207624886</v>
@@ -23055,7 +23055,7 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>12.67723139677292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -23065,7 +23065,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>153.4223756963636</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -23192,7 +23192,7 @@
         <v>264.382266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>293.6017673254133</v>
+        <v>277.3122945073554</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -23223,28 +23223,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>416.9993129555745</v>
+        <v>266.6990979018111</v>
       </c>
       <c r="C11" t="n">
-        <v>384.4745782429939</v>
+        <v>16.03629867310144</v>
       </c>
       <c r="D11" t="n">
-        <v>345.3391557398498</v>
+        <v>215.7189406860864</v>
       </c>
       <c r="E11" t="n">
-        <v>339.3632896068686</v>
+        <v>212.9886659509547</v>
       </c>
       <c r="F11" t="n">
-        <v>339.8896287080119</v>
+        <v>211.3623168800549</v>
       </c>
       <c r="G11" t="n">
-        <v>337.1211913824936</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>91.2531210150852</v>
+        <v>261.8170503391247</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>142.6493110848568</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -23274,25 +23274,25 @@
         <v>377.6409664189359</v>
       </c>
       <c r="S11" t="n">
-        <v>157.5636954405139</v>
+        <v>391.4906203878312</v>
       </c>
       <c r="T11" t="n">
-        <v>514.5131998190161</v>
+        <v>367.5080277219718</v>
       </c>
       <c r="U11" t="n">
-        <v>584.0904020762489</v>
+        <v>173.1419598303977</v>
       </c>
       <c r="V11" t="n">
-        <v>564.8510241668239</v>
+        <v>353.6557553496196</v>
       </c>
       <c r="W11" t="n">
-        <v>573.3734759809475</v>
+        <v>369.175626518582</v>
       </c>
       <c r="X11" t="n">
-        <v>527.2818334606677</v>
+        <v>345.5760270090548</v>
       </c>
       <c r="Y11" t="n">
-        <v>419.2657811628841</v>
+        <v>270.1802283817312</v>
       </c>
     </row>
     <row r="12">
@@ -23302,25 +23302,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>84.55655664632661</v>
+        <v>222.7951208435828</v>
       </c>
       <c r="C12" t="n">
-        <v>296.0999124455193</v>
+        <v>207.1075174881593</v>
       </c>
       <c r="D12" t="n">
-        <v>282.9376868977026</v>
+        <v>195.3897954627749</v>
       </c>
       <c r="E12" t="n">
-        <v>276.0587328435716</v>
+        <v>192.1409658537258</v>
       </c>
       <c r="F12" t="n">
-        <v>274.6362423378769</v>
+        <v>187.6333737802202</v>
       </c>
       <c r="G12" t="n">
-        <v>259.8641019127632</v>
+        <v>175.8112098244191</v>
       </c>
       <c r="H12" t="n">
-        <v>258.7132381298173</v>
+        <v>206.5431317313733</v>
       </c>
       <c r="I12" t="n">
         <v>139.7129300480285</v>
@@ -23350,28 +23350,28 @@
         <v>13.60608307552238</v>
       </c>
       <c r="R12" t="n">
-        <v>427.9200991791718</v>
+        <v>261.1511695487649</v>
       </c>
       <c r="S12" t="n">
-        <v>385.3031980778189</v>
+        <v>254.210749649318</v>
       </c>
       <c r="T12" t="n">
-        <v>336.8291520099667</v>
+        <v>207.9774693968605</v>
       </c>
       <c r="U12" t="n">
-        <v>335.1527654205641</v>
+        <v>157.5834551719878</v>
       </c>
       <c r="V12" t="n">
-        <v>349.5106671915202</v>
+        <v>202.6494502273624</v>
       </c>
       <c r="W12" t="n">
-        <v>367.3731429098285</v>
+        <v>223.6712367342013</v>
       </c>
       <c r="X12" t="n">
-        <v>354.8627394453875</v>
+        <v>222.4440873306922</v>
       </c>
       <c r="Y12" t="n">
-        <v>334.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -23381,76 +23381,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>222.1138003370787</v>
+        <v>178.8911437853545</v>
       </c>
       <c r="C13" t="n">
-        <v>207.7252466480447</v>
+        <v>163.1787363032171</v>
       </c>
       <c r="D13" t="n">
-        <v>220.5362180555555</v>
+        <v>175.0606502394635</v>
       </c>
       <c r="E13" t="n">
-        <v>215.9809048369565</v>
+        <v>171.2932657564968</v>
       </c>
       <c r="F13" t="n">
-        <v>209.3828559677419</v>
+        <v>163.9044306803856</v>
       </c>
       <c r="G13" t="n">
-        <v>179.3099384153005</v>
+        <v>137.0939158036555</v>
       </c>
       <c r="H13" t="n">
-        <v>157.2457818393235</v>
+        <v>144.897029286092</v>
       </c>
       <c r="I13" t="n">
         <v>111.9083503252247</v>
       </c>
       <c r="J13" t="n">
-        <v>52.58010120070892</v>
+        <v>112.3961212726902</v>
       </c>
       <c r="K13" t="n">
-        <v>138.2509377355693</v>
+        <v>59.28293637887066</v>
       </c>
       <c r="L13" t="n">
-        <v>249.4315953708939</v>
+        <v>53.87988943533696</v>
       </c>
       <c r="M13" t="n">
-        <v>340.5840540255007</v>
+        <v>45.17987151183969</v>
       </c>
       <c r="N13" t="n">
-        <v>393.8730916651275</v>
+        <v>47.00301244899811</v>
       </c>
       <c r="O13" t="n">
-        <v>471.7072689970477</v>
+        <v>43.463389140255</v>
       </c>
       <c r="P13" t="n">
-        <v>533.6818645413923</v>
+        <v>56.91632182422592</v>
       </c>
       <c r="Q13" t="n">
-        <v>599.382266425598</v>
+        <v>81.42923654054059</v>
       </c>
       <c r="R13" t="n">
-        <v>628.6017673254133</v>
+        <v>117.5896595055526</v>
       </c>
       <c r="S13" t="n">
-        <v>284.5830042930194</v>
+        <v>99.37753491274461</v>
       </c>
       <c r="T13" t="n">
-        <v>141.8886648669134</v>
+        <v>45.20585393795169</v>
       </c>
       <c r="U13" t="n">
-        <v>85.91835848757269</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>134.1703102162162</v>
+        <v>51.64314510510511</v>
       </c>
       <c r="W13" t="n">
-        <v>161.3728098387097</v>
+        <v>78.16684694982081</v>
       </c>
       <c r="X13" t="n">
-        <v>182.4436454301076</v>
+        <v>99.31214765232977</v>
       </c>
       <c r="Y13" t="n">
-        <v>222.4653528494624</v>
+        <v>139.716437516129</v>
       </c>
     </row>
     <row r="14">
@@ -23460,13 +23460,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>252.9993129555745</v>
+        <v>17.99931295557451</v>
       </c>
       <c r="C14" t="n">
-        <v>220.4745782429939</v>
+        <v>186.6077696254876</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>181.3391557398498</v>
       </c>
       <c r="E14" t="n">
         <v>175.3632896068686</v>
@@ -23478,7 +23478,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>162.2531210150852</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23511,10 +23511,10 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>228.5636954405139</v>
       </c>
       <c r="T14" t="n">
-        <v>350.5131998190162</v>
+        <v>115.5131998190162</v>
       </c>
       <c r="U14" t="n">
         <v>420.0904020762488</v>
@@ -23523,7 +23523,7 @@
         <v>400.8510241668239</v>
       </c>
       <c r="W14" t="n">
-        <v>242.6626395588901</v>
+        <v>174.3734759809475</v>
       </c>
       <c r="X14" t="n">
         <v>363.2818334606677</v>
@@ -23542,10 +23542,10 @@
         <v>155.5565566463266</v>
       </c>
       <c r="C15" t="n">
-        <v>132.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>118.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>113.6720972219126</v>
@@ -23554,10 +23554,10 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>95.86410191276319</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>94.71323812981736</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -23587,10 +23587,10 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>263.9200991791718</v>
+        <v>151.745608241793</v>
       </c>
       <c r="S15" t="n">
-        <v>221.3031980778188</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
@@ -23599,16 +23599,16 @@
         <v>171.1527654205641</v>
       </c>
       <c r="V15" t="n">
-        <v>152.8268510872038</v>
+        <v>185.5106671915202</v>
       </c>
       <c r="W15" t="n">
         <v>203.3731429098285</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>190.8627394453875</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>170.3913927661343</v>
       </c>
     </row>
     <row r="16">
@@ -23633,7 +23633,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>15.30993841530052</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -23651,13 +23651,13 @@
         <v>85.43159537089392</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>176.5840540255007</v>
       </c>
       <c r="N16" t="n">
-        <v>8.594886223040191</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>307.7072689970477</v>
+        <v>155.0280396098877</v>
       </c>
       <c r="P16" t="n">
         <v>369.6818645413923</v>
@@ -23703,19 +23703,19 @@
         <v>219.4745782429939</v>
       </c>
       <c r="D17" t="n">
-        <v>180.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>174.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
         <v>174.8896287080119</v>
       </c>
       <c r="G17" t="n">
-        <v>172.1211913824936</v>
+        <v>3.652453184811171</v>
       </c>
       <c r="H17" t="n">
-        <v>161.2531210150852</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -23751,13 +23751,13 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>114.5131998190162</v>
+        <v>349.5131998190162</v>
       </c>
       <c r="U17" t="n">
-        <v>204.6660975167627</v>
+        <v>419.0904020762488</v>
       </c>
       <c r="V17" t="n">
-        <v>164.8510241668239</v>
+        <v>399.8510241668239</v>
       </c>
       <c r="W17" t="n">
         <v>408.3734759809475</v>
@@ -23782,19 +23782,19 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>117.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>112.6720972219126</v>
       </c>
       <c r="F18" t="n">
-        <v>109.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>94.86410191276319</v>
       </c>
       <c r="H18" t="n">
-        <v>93.71323812981736</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -23827,25 +23827,25 @@
         <v>262.9200991791718</v>
       </c>
       <c r="S18" t="n">
-        <v>220.3031980778188</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>171.8291520099666</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>170.1527654205641</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>134.0998977989699</v>
       </c>
       <c r="W18" t="n">
         <v>202.3731429098285</v>
       </c>
       <c r="X18" t="n">
-        <v>54.76166613477031</v>
+        <v>189.8627394453875</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>169.3913927661343</v>
       </c>
     </row>
     <row r="19">
@@ -23855,16 +23855,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>57.11380033707866</v>
+        <v>13.73159732924446</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>55.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>50.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -23885,13 +23885,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>84.43159537089392</v>
       </c>
       <c r="M19" t="n">
         <v>175.5840540255007</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>228.8730916651275</v>
       </c>
       <c r="O19" t="n">
         <v>306.7072689970477</v>
@@ -23903,7 +23903,7 @@
         <v>434.382266425598</v>
       </c>
       <c r="R19" t="n">
-        <v>463.6017673254133</v>
+        <v>228.6017673254134</v>
       </c>
       <c r="S19" t="n">
         <v>119.5830042930194</v>
@@ -23924,7 +23924,7 @@
         <v>17.44364543010755</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>57.46535284946236</v>
       </c>
     </row>
     <row r="20">
@@ -23937,13 +23937,13 @@
         <v>16.99931295557451</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>219.4745782429939</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>13.85719506981556</v>
       </c>
       <c r="E20" t="n">
-        <v>174.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -23952,7 +23952,7 @@
         <v>172.1211913824936</v>
       </c>
       <c r="H20" t="n">
-        <v>161.2531210150852</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -23988,10 +23988,10 @@
         <v>227.5636954405139</v>
       </c>
       <c r="T20" t="n">
-        <v>349.5131998190161</v>
+        <v>349.5131998190162</v>
       </c>
       <c r="U20" t="n">
-        <v>419.0904020762489</v>
+        <v>419.0904020762488</v>
       </c>
       <c r="V20" t="n">
         <v>399.8510241668239</v>
@@ -24003,7 +24003,7 @@
         <v>362.2818334606677</v>
       </c>
       <c r="Y20" t="n">
-        <v>179.0327953736621</v>
+        <v>281.3174326828064</v>
       </c>
     </row>
     <row r="21">
@@ -24019,16 +24019,16 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>117.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>112.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>109.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>94.8641019127632</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -24064,22 +24064,22 @@
         <v>262.9200991791718</v>
       </c>
       <c r="S21" t="n">
-        <v>220.3031980778189</v>
+        <v>220.3031980778188</v>
       </c>
       <c r="T21" t="n">
-        <v>29.9864227391692</v>
+        <v>95.02497987965573</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>184.5106671915202</v>
       </c>
       <c r="W21" t="n">
         <v>202.3731429098285</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>189.8627394453875</v>
       </c>
       <c r="Y21" t="n">
         <v>169.3913927661343</v>
@@ -24101,7 +24101,7 @@
         <v>55.53621805555548</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>50.98090483695654</v>
       </c>
       <c r="F22" t="n">
         <v>44.38285596774193</v>
@@ -24122,7 +24122,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>84.43159537089389</v>
+        <v>84.43159537089392</v>
       </c>
       <c r="M22" t="n">
         <v>175.5840540255007</v>
@@ -24131,16 +24131,16 @@
         <v>228.8730916651275</v>
       </c>
       <c r="O22" t="n">
-        <v>306.7072689970478</v>
+        <v>306.7072689970477</v>
       </c>
       <c r="P22" t="n">
         <v>368.6818645413923</v>
       </c>
       <c r="Q22" t="n">
-        <v>410.9602917365661</v>
+        <v>199.382266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>228.6017673254133</v>
+        <v>381.5989785801465</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -24171,25 +24171,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>251.9993129555745</v>
+        <v>69.9919305285342</v>
       </c>
       <c r="C23" t="n">
-        <v>219.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>180.3391557398498</v>
       </c>
       <c r="E23" t="n">
-        <v>174.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>85.36197583035532</v>
+        <v>172.1211913824936</v>
       </c>
       <c r="H23" t="n">
-        <v>161.2531210150852</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -24225,22 +24225,22 @@
         <v>227.5636954405139</v>
       </c>
       <c r="T23" t="n">
-        <v>349.5131998190161</v>
+        <v>349.5131998190162</v>
       </c>
       <c r="U23" t="n">
-        <v>419.0904020762489</v>
+        <v>419.0904020762488</v>
       </c>
       <c r="V23" t="n">
         <v>399.8510241668239</v>
       </c>
       <c r="W23" t="n">
-        <v>173.3734759809475</v>
+        <v>408.3734759809475</v>
       </c>
       <c r="X23" t="n">
         <v>362.2818334606677</v>
       </c>
       <c r="Y23" t="n">
-        <v>46.31743268280638</v>
+        <v>281.3174326828064</v>
       </c>
     </row>
     <row r="24">
@@ -24250,10 +24250,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>154.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>131.0999124455193</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -24265,10 +24265,10 @@
         <v>109.6362423378769</v>
       </c>
       <c r="G24" t="n">
-        <v>94.8641019127632</v>
+        <v>94.86410191276319</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>93.71323812981736</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -24298,19 +24298,19 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>262.9200991791718</v>
+        <v>27.92009917917173</v>
       </c>
       <c r="S24" t="n">
-        <v>176.3853215004592</v>
+        <v>220.3031980778188</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>139.0566288748284</v>
       </c>
       <c r="V24" t="n">
-        <v>184.5106671915202</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>202.3731429098285</v>
@@ -24319,7 +24319,7 @@
         <v>189.8627394453875</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>169.3913927661343</v>
       </c>
     </row>
     <row r="25">
@@ -24329,22 +24329,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>57.11380033707866</v>
       </c>
       <c r="C25" t="n">
         <v>42.72524664804467</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>55.53621805555548</v>
       </c>
       <c r="E25" t="n">
         <v>50.98090483695654</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>44.38285596774193</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>14.30993841530052</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -24359,16 +24359,16 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>84.43159537089389</v>
+        <v>84.43159537089392</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>228.8730916651275</v>
+        <v>167.4497171744955</v>
       </c>
       <c r="O25" t="n">
-        <v>306.7072689970478</v>
+        <v>306.7072689970477</v>
       </c>
       <c r="P25" t="n">
         <v>368.6818645413923</v>
@@ -24377,10 +24377,10 @@
         <v>434.382266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>463.6017673254133</v>
+        <v>228.6017673254134</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>119.5830042930194</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24414,16 +24414,16 @@
         <v>266.4745782429939</v>
       </c>
       <c r="D26" t="n">
-        <v>131.3188668247084</v>
+        <v>227.3391557398498</v>
       </c>
       <c r="E26" t="n">
-        <v>84.36328960686831</v>
+        <v>221.3632896068686</v>
       </c>
       <c r="F26" t="n">
-        <v>84.8896287080114</v>
+        <v>221.8896287080119</v>
       </c>
       <c r="G26" t="n">
-        <v>219.1211913824936</v>
+        <v>82.12119138249261</v>
       </c>
       <c r="H26" t="n">
         <v>71.25312101508422</v>
@@ -24462,10 +24462,10 @@
         <v>274.5636954405139</v>
       </c>
       <c r="T26" t="n">
-        <v>396.5131998190161</v>
+        <v>259.5131998190153</v>
       </c>
       <c r="U26" t="n">
-        <v>466.0904020762489</v>
+        <v>370.0701131611085</v>
       </c>
       <c r="V26" t="n">
         <v>446.8510241668239</v>
@@ -24490,13 +24490,13 @@
         <v>201.5565566463266</v>
       </c>
       <c r="C27" t="n">
-        <v>41.09991244551884</v>
+        <v>41.09991244551918</v>
       </c>
       <c r="D27" t="n">
-        <v>164.9376868977026</v>
+        <v>27.93768689770206</v>
       </c>
       <c r="E27" t="n">
-        <v>159.6720972219126</v>
+        <v>40.74143547249561</v>
       </c>
       <c r="F27" t="n">
         <v>156.6362423378769</v>
@@ -24544,7 +24544,7 @@
         <v>218.8291520099667</v>
       </c>
       <c r="U27" t="n">
-        <v>80.15276542056301</v>
+        <v>217.1527654205641</v>
       </c>
       <c r="V27" t="n">
         <v>231.5106671915202</v>
@@ -24556,7 +24556,7 @@
         <v>236.8627394453875</v>
       </c>
       <c r="Y27" t="n">
-        <v>79.391392766134</v>
+        <v>216.3913927661343</v>
       </c>
     </row>
     <row r="28">
@@ -24584,7 +24584,7 @@
         <v>61.30993841530054</v>
       </c>
       <c r="H28" t="n">
-        <v>39.24578183932354</v>
+        <v>21.14588125540044</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -24614,7 +24614,7 @@
         <v>481.382266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>464.8812442625952</v>
+        <v>510.6017673254133</v>
       </c>
       <c r="S28" t="n">
         <v>166.5830042930194</v>
@@ -24626,10 +24626,10 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>16.17031021621619</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>43.37280983870968</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>64.44364543010755</v>
@@ -24648,19 +24648,19 @@
         <v>280.9993129555745</v>
       </c>
       <c r="C29" t="n">
-        <v>111.4745782429931</v>
+        <v>111.4745782429935</v>
       </c>
       <c r="D29" t="n">
-        <v>72.33915573984899</v>
+        <v>209.3391557398498</v>
       </c>
       <c r="E29" t="n">
-        <v>66.36328960686791</v>
+        <v>203.3632896068686</v>
       </c>
       <c r="F29" t="n">
         <v>203.8896287080119</v>
       </c>
       <c r="G29" t="n">
-        <v>80.45159138249593</v>
+        <v>64.12119138249233</v>
       </c>
       <c r="H29" t="n">
         <v>190.2531210150852</v>
@@ -24702,7 +24702,7 @@
         <v>378.5131998190162</v>
       </c>
       <c r="U29" t="n">
-        <v>448.0904020762488</v>
+        <v>311.0904020762476</v>
       </c>
       <c r="V29" t="n">
         <v>428.8510241668239</v>
@@ -24711,7 +24711,7 @@
         <v>437.3734759809475</v>
       </c>
       <c r="X29" t="n">
-        <v>391.2818334606677</v>
+        <v>270.6122334606708</v>
       </c>
       <c r="Y29" t="n">
         <v>310.3174326828064</v>
@@ -24724,7 +24724,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>46.55655664632599</v>
+        <v>174.9850369669335</v>
       </c>
       <c r="C30" t="n">
         <v>160.0999124455193</v>
@@ -24736,10 +24736,10 @@
         <v>141.6720972219126</v>
       </c>
       <c r="F30" t="n">
-        <v>1.636242337876126</v>
+        <v>138.6362423378769</v>
       </c>
       <c r="G30" t="n">
-        <v>123.8641019127632</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -24781,10 +24781,10 @@
         <v>200.8291520099666</v>
       </c>
       <c r="U30" t="n">
-        <v>199.1527654205641</v>
+        <v>62.15276542056296</v>
       </c>
       <c r="V30" t="n">
-        <v>213.5106671915202</v>
+        <v>76.51066719151964</v>
       </c>
       <c r="W30" t="n">
         <v>231.3731429098285</v>
@@ -24793,7 +24793,7 @@
         <v>218.8627394453875</v>
       </c>
       <c r="Y30" t="n">
-        <v>65.95577117397727</v>
+        <v>198.3913927661343</v>
       </c>
     </row>
     <row r="31">
@@ -24809,7 +24809,7 @@
         <v>71.72524664804467</v>
       </c>
       <c r="D31" t="n">
-        <v>84.53621805555548</v>
+        <v>58.98022630545458</v>
       </c>
       <c r="E31" t="n">
         <v>79.98090483695654</v>
@@ -24833,7 +24833,7 @@
         <v>2.250937735569295</v>
       </c>
       <c r="L31" t="n">
-        <v>56.61412891516953</v>
+        <v>113.4315953708939</v>
       </c>
       <c r="M31" t="n">
         <v>204.5840540255007</v>
@@ -24851,13 +24851,13 @@
         <v>463.382266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>355.6017673254133</v>
+        <v>492.6017673254133</v>
       </c>
       <c r="S31" t="n">
-        <v>148.5830042930194</v>
+        <v>11.58300429301937</v>
       </c>
       <c r="T31" t="n">
-        <v>5.888664866913452</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -24866,7 +24866,7 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>25.37280983870968</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
         <v>46.44364543010755</v>
@@ -24888,7 +24888,7 @@
         <v>248.4745782429939</v>
       </c>
       <c r="D32" t="n">
-        <v>72.33915573984922</v>
+        <v>209.3391557398498</v>
       </c>
       <c r="E32" t="n">
         <v>203.3632896068686</v>
@@ -24933,19 +24933,19 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>119.5636954405127</v>
+        <v>135.8940954405164</v>
       </c>
       <c r="T32" t="n">
-        <v>257.8435998190188</v>
+        <v>378.5131998190161</v>
       </c>
       <c r="U32" t="n">
-        <v>448.0904020762489</v>
+        <v>311.0904020762477</v>
       </c>
       <c r="V32" t="n">
         <v>428.8510241668239</v>
       </c>
       <c r="W32" t="n">
-        <v>437.3734759809475</v>
+        <v>300.3734759809471</v>
       </c>
       <c r="X32" t="n">
         <v>391.2818334606677</v>
@@ -24970,13 +24970,13 @@
         <v>146.9376868977026</v>
       </c>
       <c r="E33" t="n">
-        <v>4.672097221911997</v>
+        <v>141.6720972219126</v>
       </c>
       <c r="F33" t="n">
-        <v>1.636242337876354</v>
+        <v>138.6362423378769</v>
       </c>
       <c r="G33" t="n">
-        <v>5.715242190790491</v>
+        <v>123.8641019127632</v>
       </c>
       <c r="H33" t="n">
         <v>122.7132381298173</v>
@@ -25009,25 +25009,25 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>154.9200991791704</v>
+        <v>173.7712394571982</v>
       </c>
       <c r="S33" t="n">
         <v>249.3031980778189</v>
       </c>
       <c r="T33" t="n">
-        <v>200.8291520099667</v>
+        <v>63.82915200996575</v>
       </c>
       <c r="U33" t="n">
         <v>199.1527654205641</v>
       </c>
       <c r="V33" t="n">
-        <v>213.5106671915202</v>
+        <v>76.51066719151976</v>
       </c>
       <c r="W33" t="n">
         <v>231.3731429098285</v>
       </c>
       <c r="X33" t="n">
-        <v>218.8627394453875</v>
+        <v>81.86273944538715</v>
       </c>
       <c r="Y33" t="n">
         <v>198.3913927661343</v>
@@ -25040,10 +25040,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>86.11380033707866</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>71.72524664804467</v>
       </c>
       <c r="D34" t="n">
         <v>84.53621805555548</v>
@@ -25055,10 +25055,10 @@
         <v>73.38285596774193</v>
       </c>
       <c r="G34" t="n">
-        <v>32.52938253548238</v>
+        <v>43.30993841530054</v>
       </c>
       <c r="H34" t="n">
-        <v>21.24578183932354</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -25085,16 +25085,16 @@
         <v>397.6818645413923</v>
       </c>
       <c r="Q34" t="n">
-        <v>463.382266425598</v>
+        <v>437.826274675496</v>
       </c>
       <c r="R34" t="n">
-        <v>492.6017673254133</v>
+        <v>355.6017673254133</v>
       </c>
       <c r="S34" t="n">
         <v>148.5830042930194</v>
       </c>
       <c r="T34" t="n">
-        <v>5.888664866913444</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -25103,10 +25103,10 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>25.37280983870968</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>46.44364543010755</v>
       </c>
       <c r="Y34" t="n">
         <v>86.46535284946236</v>
@@ -25125,19 +25125,19 @@
         <v>248.4745782429939</v>
       </c>
       <c r="D35" t="n">
-        <v>72.33915573984922</v>
+        <v>209.3391557398498</v>
       </c>
       <c r="E35" t="n">
-        <v>66.36328960686814</v>
+        <v>66.36328960686791</v>
       </c>
       <c r="F35" t="n">
         <v>203.8896287080119</v>
       </c>
       <c r="G35" t="n">
-        <v>64.12119138249267</v>
+        <v>201.1211913824936</v>
       </c>
       <c r="H35" t="n">
-        <v>69.5835210150872</v>
+        <v>53.25312101508399</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -25170,10 +25170,10 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>256.5636954405139</v>
+        <v>119.5636954405125</v>
       </c>
       <c r="T35" t="n">
-        <v>378.5131998190161</v>
+        <v>257.8435998190195</v>
       </c>
       <c r="U35" t="n">
         <v>448.0904020762489</v>
@@ -25198,25 +25198,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>46.55655664632621</v>
+        <v>183.5565566463266</v>
       </c>
       <c r="C36" t="n">
         <v>160.0999124455193</v>
       </c>
       <c r="D36" t="n">
-        <v>146.9376868977026</v>
+        <v>9.937686897701894</v>
       </c>
       <c r="E36" t="n">
-        <v>141.6720972219126</v>
+        <v>4.67209722191177</v>
       </c>
       <c r="F36" t="n">
-        <v>138.6362423378769</v>
+        <v>6.200620745720698</v>
       </c>
       <c r="G36" t="n">
         <v>123.8641019127632</v>
       </c>
       <c r="H36" t="n">
-        <v>122.7132381298173</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -25252,10 +25252,10 @@
         <v>249.3031980778189</v>
       </c>
       <c r="T36" t="n">
-        <v>63.82915200996575</v>
+        <v>200.8291520099667</v>
       </c>
       <c r="U36" t="n">
-        <v>62.15276542056307</v>
+        <v>199.1527654205641</v>
       </c>
       <c r="V36" t="n">
         <v>213.5106671915202</v>
@@ -25267,7 +25267,7 @@
         <v>218.8627394453875</v>
       </c>
       <c r="Y36" t="n">
-        <v>80.24253304416068</v>
+        <v>198.3913927661343</v>
       </c>
     </row>
     <row r="37">
@@ -25277,7 +25277,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4.134496569524472</v>
+        <v>86.11380033707866</v>
       </c>
       <c r="C37" t="n">
         <v>71.72524664804467</v>
@@ -25307,10 +25307,10 @@
         <v>2.250937735569295</v>
       </c>
       <c r="L37" t="n">
-        <v>113.4315953708939</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>204.5840540255007</v>
+        <v>155.4596576462922</v>
       </c>
       <c r="N37" t="n">
         <v>257.8730916651275</v>
@@ -25331,7 +25331,7 @@
         <v>148.5830042930194</v>
       </c>
       <c r="T37" t="n">
-        <v>5.888664866913444</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -25346,7 +25346,7 @@
         <v>46.44364543010755</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>86.46535284946236</v>
       </c>
     </row>
     <row r="38">
@@ -25359,13 +25359,13 @@
         <v>280.9993129555745</v>
       </c>
       <c r="C38" t="n">
-        <v>127.8049782429977</v>
+        <v>248.4745782429939</v>
       </c>
       <c r="D38" t="n">
         <v>209.3391557398498</v>
       </c>
       <c r="E38" t="n">
-        <v>66.36328960686791</v>
+        <v>203.3632896068686</v>
       </c>
       <c r="F38" t="n">
         <v>203.8896287080119</v>
@@ -25374,7 +25374,7 @@
         <v>201.1211913824936</v>
       </c>
       <c r="H38" t="n">
-        <v>53.25312101508376</v>
+        <v>190.2531210150852</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -25407,16 +25407,16 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>119.5636954405123</v>
+        <v>119.5636954405126</v>
       </c>
       <c r="T38" t="n">
-        <v>378.5131998190162</v>
+        <v>241.513199819015</v>
       </c>
       <c r="U38" t="n">
-        <v>448.0904020762488</v>
+        <v>311.0904020762476</v>
       </c>
       <c r="V38" t="n">
-        <v>428.8510241668239</v>
+        <v>308.1814241668275</v>
       </c>
       <c r="W38" t="n">
         <v>437.3734759809475</v>
@@ -25453,7 +25453,7 @@
         <v>123.8641019127632</v>
       </c>
       <c r="H39" t="n">
-        <v>4.564378407844986</v>
+        <v>122.7132381298173</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -25486,25 +25486,25 @@
         <v>291.9200991791718</v>
       </c>
       <c r="S39" t="n">
-        <v>249.3031980778188</v>
+        <v>249.3031980778189</v>
       </c>
       <c r="T39" t="n">
-        <v>63.82915200996553</v>
+        <v>200.8291520099667</v>
       </c>
       <c r="U39" t="n">
-        <v>62.15276542056284</v>
+        <v>199.1527654205641</v>
       </c>
       <c r="V39" t="n">
-        <v>76.51066719151953</v>
+        <v>76.51066719151964</v>
       </c>
       <c r="W39" t="n">
-        <v>231.3731429098285</v>
+        <v>94.373142909828</v>
       </c>
       <c r="X39" t="n">
-        <v>218.8627394453875</v>
+        <v>100.713879723414</v>
       </c>
       <c r="Y39" t="n">
-        <v>198.3913927661343</v>
+        <v>61.39139276613383</v>
       </c>
     </row>
     <row r="40">
@@ -25529,7 +25529,7 @@
         <v>73.38285596774193</v>
       </c>
       <c r="G40" t="n">
-        <v>43.30993841530052</v>
+        <v>43.30993841530054</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -25544,7 +25544,7 @@
         <v>2.250937735569295</v>
       </c>
       <c r="L40" t="n">
-        <v>113.4315953708939</v>
+        <v>109.0662031182985</v>
       </c>
       <c r="M40" t="n">
         <v>204.5840540255007</v>
@@ -25553,7 +25553,7 @@
         <v>257.8730916651275</v>
       </c>
       <c r="O40" t="n">
-        <v>335.7072689970477</v>
+        <v>335.7072689970478</v>
       </c>
       <c r="P40" t="n">
         <v>397.6818645413923</v>
@@ -25565,7 +25565,7 @@
         <v>492.6017673254133</v>
       </c>
       <c r="S40" t="n">
-        <v>57.75225919096246</v>
+        <v>148.5830042930194</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -25583,7 +25583,7 @@
         <v>46.44364543010755</v>
       </c>
       <c r="Y40" t="n">
-        <v>86.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -25608,13 +25608,13 @@
         <v>221.8896287080119</v>
       </c>
       <c r="G41" t="n">
-        <v>82.12119138249227</v>
+        <v>219.1211913824936</v>
       </c>
       <c r="H41" t="n">
-        <v>71.25312101508388</v>
+        <v>208.2531210150852</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>24.64931108485681</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -25650,16 +25650,16 @@
         <v>396.5131998190162</v>
       </c>
       <c r="U41" t="n">
-        <v>370.070113161109</v>
+        <v>329.0904020762476</v>
       </c>
       <c r="V41" t="n">
-        <v>309.8510241668232</v>
+        <v>326.1814241668262</v>
       </c>
       <c r="W41" t="n">
-        <v>455.3734759809475</v>
+        <v>318.3734759809471</v>
       </c>
       <c r="X41" t="n">
-        <v>409.2818334606677</v>
+        <v>272.2818334606671</v>
       </c>
       <c r="Y41" t="n">
         <v>328.3174326828064</v>
@@ -25672,10 +25672,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>64.55655664632582</v>
+        <v>201.5565566463266</v>
       </c>
       <c r="C42" t="n">
-        <v>41.09991244551861</v>
+        <v>178.0999124455193</v>
       </c>
       <c r="D42" t="n">
         <v>164.9376868977026</v>
@@ -25684,16 +25684,16 @@
         <v>159.6720972219126</v>
       </c>
       <c r="F42" t="n">
-        <v>156.6362423378769</v>
+        <v>19.6362423378763</v>
       </c>
       <c r="G42" t="n">
-        <v>141.8641019127632</v>
+        <v>4.864101912762067</v>
       </c>
       <c r="H42" t="n">
         <v>140.7132381298174</v>
       </c>
       <c r="I42" t="n">
-        <v>21.71293004802855</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -25720,7 +25720,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>288.4784601102193</v>
+        <v>309.9200991791718</v>
       </c>
       <c r="S42" t="n">
         <v>267.3031980778189</v>
@@ -25729,10 +25729,10 @@
         <v>218.8291520099666</v>
       </c>
       <c r="U42" t="n">
-        <v>217.1527654205641</v>
+        <v>87.97687692553046</v>
       </c>
       <c r="V42" t="n">
-        <v>94.51066719151959</v>
+        <v>231.5106671915202</v>
       </c>
       <c r="W42" t="n">
         <v>249.3731429098285</v>
@@ -25796,7 +25796,7 @@
         <v>415.6818645413923</v>
       </c>
       <c r="Q43" t="n">
-        <v>411.2937977661655</v>
+        <v>481.382266425598</v>
       </c>
       <c r="R43" t="n">
         <v>510.6017673254133</v>
@@ -25805,16 +25805,16 @@
         <v>166.5830042930194</v>
       </c>
       <c r="T43" t="n">
-        <v>23.88866486691345</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>16.17031021621619</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>43.37280983870968</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
         <v>64.44364543010755</v>
@@ -25830,10 +25830,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>331.372464735982</v>
+        <v>193.6990979018108</v>
       </c>
       <c r="C44" t="n">
-        <v>315.0362986731014</v>
+        <v>178.0362986731012</v>
       </c>
       <c r="D44" t="n">
         <v>279.7189406860864</v>
@@ -25845,7 +25845,7 @@
         <v>275.3623168800549</v>
       </c>
       <c r="G44" t="n">
-        <v>277.9092564389587</v>
+        <v>140.9092564389583</v>
       </c>
       <c r="H44" t="n">
         <v>325.8170503391247</v>
@@ -25863,10 +25863,10 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>118.9630773910598</v>
+        <v>255.963077391061</v>
       </c>
       <c r="N44" t="n">
-        <v>47.30110882360259</v>
+        <v>47.30110882360282</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -25878,25 +25878,25 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>304.6409664189349</v>
+        <v>441.6409664189359</v>
       </c>
       <c r="S44" t="n">
-        <v>318.4906203878304</v>
+        <v>455.4906203878312</v>
       </c>
       <c r="T44" t="n">
-        <v>431.5080277219718</v>
+        <v>336.864054353663</v>
       </c>
       <c r="U44" t="n">
         <v>447.49127093668</v>
       </c>
       <c r="V44" t="n">
-        <v>417.6557553496196</v>
+        <v>418.3291221837904</v>
       </c>
       <c r="W44" t="n">
         <v>433.175626518582</v>
       </c>
       <c r="X44" t="n">
-        <v>314.9320536407479</v>
+        <v>409.5760270090548</v>
       </c>
       <c r="Y44" t="n">
         <v>334.1802283817312</v>
@@ -25924,13 +25924,13 @@
         <v>251.6333737802202</v>
       </c>
       <c r="G45" t="n">
-        <v>102.8112098244184</v>
+        <v>239.8112098244191</v>
       </c>
       <c r="H45" t="n">
         <v>270.5431317313733</v>
       </c>
       <c r="I45" t="n">
-        <v>122.6463900390462</v>
+        <v>203.7129300480285</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25945,7 +25945,7 @@
         <v>161.9297782656032</v>
       </c>
       <c r="N45" t="n">
-        <v>122.0961940438275</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -25957,7 +25957,7 @@
         <v>77.60608307552238</v>
       </c>
       <c r="R45" t="n">
-        <v>325.1511695487649</v>
+        <v>229.1808235836094</v>
       </c>
       <c r="S45" t="n">
         <v>318.2107496493181</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1119782.036784445</v>
+        <v>1119782.036784446</v>
       </c>
     </row>
     <row r="3">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3398048.358864671</v>
+        <v>3671589.294467091</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4202967.168384287</v>
+        <v>4476508.103986705</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4984847.189956388</v>
+        <v>5258388.125558807</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5765555.874385632</v>
+        <v>6039096.809988044</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6546264.558814871</v>
+        <v>6819805.49441728</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7139417.316144249</v>
+        <v>7412958.251746658</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7843066.675029115</v>
+        <v>8116607.610631526</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8525888.568596441</v>
+        <v>8799429.504198851</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9208710.462163769</v>
+        <v>9482251.397766178</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>9891532.355731098</v>
+        <v>10165073.2913335</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10492611.36174074</v>
+        <v>10766152.29734314</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>10954576.05840203</v>
+        <v>11228116.99400443</v>
       </c>
     </row>
   </sheetData>
@@ -26281,25 +26281,25 @@
         <v>384532.7075366525</v>
       </c>
       <c r="F2" t="n">
-        <v>823062.1051743594</v>
+        <v>823062.1051743592</v>
       </c>
       <c r="G2" t="n">
+        <v>826632.7246897871</v>
+      </c>
+      <c r="H2" t="n">
         <v>826632.7246897868</v>
       </c>
-      <c r="H2" t="n">
-        <v>826632.7246897869</v>
-      </c>
       <c r="I2" t="n">
-        <v>826632.7246897869</v>
+        <v>826632.7246897868</v>
       </c>
       <c r="J2" t="n">
-        <v>658489.2049346657</v>
+        <v>658489.2049346655</v>
       </c>
       <c r="K2" t="n">
-        <v>722987.8873065888</v>
+        <v>722987.8873065887</v>
       </c>
       <c r="L2" t="n">
-        <v>722987.8873065887</v>
+        <v>722987.8873065886</v>
       </c>
       <c r="M2" t="n">
         <v>722987.8873065885</v>
@@ -26308,7 +26308,7 @@
         <v>722987.8873065886</v>
       </c>
       <c r="O2" t="n">
-        <v>658489.2049346652</v>
+        <v>658489.2049346655</v>
       </c>
       <c r="P2" t="n">
         <v>199507.5117093988</v>
@@ -26373,46 +26373,46 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>586530.4930416713</v>
+        <v>586430.1509567276</v>
       </c>
       <c r="C4" t="n">
-        <v>584612.3495728398</v>
+        <v>584512.0074878959</v>
       </c>
       <c r="D4" t="n">
-        <v>582691.6040226705</v>
+        <v>582591.2619377268</v>
       </c>
       <c r="E4" t="n">
         <v>103268.7819718726</v>
       </c>
       <c r="F4" t="n">
-        <v>389628.8667981265</v>
+        <v>389603.2771202232</v>
       </c>
       <c r="G4" t="n">
-        <v>390892.9217162045</v>
+        <v>390866.2453248407</v>
       </c>
       <c r="H4" t="n">
-        <v>389401.2272093858</v>
+        <v>389374.5508180219</v>
       </c>
       <c r="I4" t="n">
-        <v>387907.450272824</v>
+        <v>387880.7738814601</v>
       </c>
       <c r="J4" t="n">
         <v>284539.4136462387</v>
       </c>
       <c r="K4" t="n">
-        <v>332033.9367601047</v>
+        <v>332014.6139826725</v>
       </c>
       <c r="L4" t="n">
-        <v>330722.9661060228</v>
+        <v>330703.6433285907</v>
       </c>
       <c r="M4" t="n">
-        <v>329410.1217196162</v>
+        <v>329390.798942184</v>
       </c>
       <c r="N4" t="n">
-        <v>328095.3896812886</v>
+        <v>328076.0669038564</v>
       </c>
       <c r="O4" t="n">
-        <v>278562.9691156339</v>
+        <v>278562.9691156338</v>
       </c>
       <c r="P4" t="n">
         <v>1608.690656871744</v>
@@ -26477,46 +26477,46 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-51730.07673890777</v>
+        <v>-51629.73465396352</v>
       </c>
       <c r="C6" t="n">
-        <v>429733.0667299245</v>
+        <v>429833.4088148679</v>
       </c>
       <c r="D6" t="n">
-        <v>431653.8122800935</v>
+        <v>431754.1543650373</v>
       </c>
       <c r="E6" t="n">
-        <v>200638.8405647799</v>
+        <v>200638.8405647798</v>
       </c>
       <c r="F6" t="n">
-        <v>259820.8373762329</v>
+        <v>259846.4270541359</v>
       </c>
       <c r="G6" t="n">
-        <v>392443.3329735823</v>
+        <v>392470.0093649464</v>
       </c>
       <c r="H6" t="n">
-        <v>394735.0274804011</v>
+        <v>394761.7038717648</v>
       </c>
       <c r="I6" t="n">
-        <v>396228.8044169629</v>
+        <v>396255.4808083267</v>
       </c>
       <c r="J6" t="n">
-        <v>278738.964288427</v>
+        <v>278738.9642884268</v>
       </c>
       <c r="K6" t="n">
-        <v>211253.8815464842</v>
+        <v>211273.2043239162</v>
       </c>
       <c r="L6" t="n">
-        <v>357364.8522005659</v>
+        <v>357384.1749779979</v>
       </c>
       <c r="M6" t="n">
-        <v>359477.6965869722</v>
+        <v>359497.0193644044</v>
       </c>
       <c r="N6" t="n">
-        <v>360792.4286253</v>
+        <v>360811.7514027322</v>
       </c>
       <c r="O6" t="n">
-        <v>347339.4088190314</v>
+        <v>347339.4088190317</v>
       </c>
       <c r="P6" t="n">
         <v>180612.5520525271</v>
@@ -26651,7 +26651,7 @@
         <v>440</v>
       </c>
       <c r="E3" t="n">
-        <v>440</v>
+        <v>-0</v>
       </c>
       <c r="F3" t="n">
         <v>440</v>
@@ -26990,7 +26990,7 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -27481,7 +27481,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>61.46597976850363</v>
+        <v>148.0998500845758</v>
       </c>
       <c r="S2" t="n">
         <v>400</v>
@@ -27557,13 +27557,13 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>61.330887731989</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>400</v>
       </c>
       <c r="S3" t="n">
-        <v>370.4375921767858</v>
+        <v>231.1418865456826</v>
       </c>
       <c r="T3" t="n">
         <v>400</v>
@@ -27572,16 +27572,16 @@
         <v>165.1527654205641</v>
       </c>
       <c r="V3" t="n">
-        <v>179.5106671915202</v>
+        <v>400</v>
       </c>
       <c r="W3" t="n">
         <v>400</v>
       </c>
       <c r="X3" t="n">
-        <v>184.8627394453875</v>
+        <v>400</v>
       </c>
       <c r="Y3" t="n">
-        <v>399.3913927661343</v>
+        <v>164.3913927661343</v>
       </c>
     </row>
     <row r="4">
@@ -27639,7 +27639,7 @@
         <v>400</v>
       </c>
       <c r="R4" t="n">
-        <v>400</v>
+        <v>112.6643301183643</v>
       </c>
       <c r="S4" t="n">
         <v>349.5830042930194</v>
@@ -27755,10 +27755,10 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>112.9376868977026</v>
+        <v>185.2948548892279</v>
       </c>
       <c r="E6" t="n">
-        <v>107.6720972219126</v>
+        <v>251.2327847396485</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
@@ -27794,13 +27794,13 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>61.330887731989</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>257.9200991791718</v>
       </c>
       <c r="S6" t="n">
-        <v>312.0436650550859</v>
+        <v>215.3031980778188</v>
       </c>
       <c r="T6" t="n">
         <v>400</v>
@@ -27809,7 +27809,7 @@
         <v>400</v>
       </c>
       <c r="V6" t="n">
-        <v>400</v>
+        <v>179.5106671915202</v>
       </c>
       <c r="W6" t="n">
         <v>400</v>
@@ -27876,7 +27876,7 @@
         <v>400</v>
       </c>
       <c r="R7" t="n">
-        <v>112.6643301183635</v>
+        <v>400</v>
       </c>
       <c r="S7" t="n">
         <v>349.5830042930194</v>
@@ -27958,7 +27958,7 @@
         <v>148.0998500845758</v>
       </c>
       <c r="S8" t="n">
-        <v>400</v>
+        <v>313.3661296839286</v>
       </c>
       <c r="T8" t="n">
         <v>400</v>
@@ -27986,7 +27986,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>231.1341809499631</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
         <v>361.0999124455193</v>
@@ -27998,7 +27998,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>104.6362423378769</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
         <v>324.8641019127632</v>
@@ -28007,7 +28007,7 @@
         <v>323.7132381298173</v>
       </c>
       <c r="I9" t="n">
-        <v>186.9853481554995</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28031,7 +28031,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>61.330887731989</v>
       </c>
       <c r="R9" t="n">
         <v>257.9200991791718</v>
@@ -28046,13 +28046,13 @@
         <v>400</v>
       </c>
       <c r="V9" t="n">
-        <v>400</v>
+        <v>213.7258151327665</v>
       </c>
       <c r="W9" t="n">
         <v>400</v>
       </c>
       <c r="X9" t="n">
-        <v>323.0713547092561</v>
+        <v>400</v>
       </c>
       <c r="Y9" t="n">
         <v>399.3913927661343</v>
@@ -28074,7 +28074,7 @@
         <v>285.5362180555555</v>
       </c>
       <c r="E10" t="n">
-        <v>264.6914320188986</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
         <v>274.3828559677419</v>
@@ -28180,7 +28180,7 @@
         <v>65</v>
       </c>
       <c r="N11" t="n">
-        <v>45.44239505953796</v>
+        <v>65</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -28326,7 +28326,7 @@
         <v>65</v>
       </c>
       <c r="J13" t="n">
-        <v>65</v>
+        <v>5.183979928018705</v>
       </c>
       <c r="K13" t="n">
         <v>65</v>
@@ -28359,7 +28359,7 @@
         <v>65</v>
       </c>
       <c r="U13" t="n">
-        <v>65</v>
+        <v>59.94996368611553</v>
       </c>
       <c r="V13" t="n">
         <v>65</v>
@@ -28414,10 +28414,10 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>229</v>
+        <v>197.4283236311547</v>
       </c>
       <c r="N14" t="n">
-        <v>153.7294324547587</v>
+        <v>185.3011088236041</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -28429,7 +28429,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>229</v>
+        <v>148.0998500845758</v>
       </c>
       <c r="S14" t="n">
         <v>229</v>
@@ -28481,25 +28481,25 @@
         <v>229</v>
       </c>
       <c r="I15" t="n">
-        <v>204.7129300480285</v>
+        <v>229</v>
       </c>
       <c r="J15" t="n">
-        <v>211.259461833694</v>
+        <v>19.54682436935798</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>85.29716164555937</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>162.9297782656032</v>
+        <v>229</v>
       </c>
       <c r="N15" t="n">
         <v>229</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>167.936767464195</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -28651,10 +28651,10 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>230</v>
+        <v>197.4283236311547</v>
       </c>
       <c r="N17" t="n">
-        <v>152.7294324547587</v>
+        <v>185.3011088236041</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -28666,7 +28666,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>230</v>
+        <v>200.897398025985</v>
       </c>
       <c r="S17" t="n">
         <v>230</v>
@@ -28721,22 +28721,22 @@
         <v>230</v>
       </c>
       <c r="J18" t="n">
+        <v>19.54682436935798</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>230</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>134.4301896302407</v>
       </c>
       <c r="N18" t="n">
         <v>230</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>167.936767464195</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -28797,10 +28797,10 @@
         <v>230</v>
       </c>
       <c r="I19" t="n">
-        <v>215.5838322468499</v>
+        <v>230</v>
       </c>
       <c r="J19" t="n">
-        <v>230</v>
+        <v>218.3797849014816</v>
       </c>
       <c r="K19" t="n">
         <v>230</v>
@@ -28888,10 +28888,10 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>230</v>
+        <v>197.4283236311547</v>
       </c>
       <c r="N20" t="n">
-        <v>152.7294324547587</v>
+        <v>185.3011088236041</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -28958,25 +28958,25 @@
         <v>230</v>
       </c>
       <c r="J21" t="n">
-        <v>230</v>
+        <v>19.54682436935798</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>66.124012589047</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>230</v>
       </c>
       <c r="N21" t="n">
-        <v>123.0961940438275</v>
+        <v>230</v>
       </c>
       <c r="O21" t="n">
         <v>167.936767464195</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>165.2842021725676</v>
       </c>
       <c r="Q21" t="n">
         <v>230</v>
@@ -29031,7 +29031,7 @@
         <v>230</v>
       </c>
       <c r="H22" t="n">
-        <v>222.2457818393235</v>
+        <v>230</v>
       </c>
       <c r="I22" t="n">
         <v>230</v>
@@ -29125,10 +29125,10 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>216.1434129203651</v>
+        <v>197.4283236311547</v>
       </c>
       <c r="N23" t="n">
-        <v>125.7663550636977</v>
+        <v>185.3011088236041</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>230</v>
+        <v>148.0998500845758</v>
       </c>
       <c r="S23" t="n">
         <v>230</v>
@@ -29195,25 +29195,25 @@
         <v>230</v>
       </c>
       <c r="J24" t="n">
-        <v>19.54682436935798</v>
+        <v>230</v>
       </c>
       <c r="K24" t="n">
-        <v>198.4129994297693</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>158.9174422431866</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>162.9297782656032</v>
+        <v>230</v>
       </c>
       <c r="N24" t="n">
-        <v>123.0961940438275</v>
+        <v>230</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>56.60351674242489</v>
       </c>
       <c r="Q24" t="n">
         <v>230</v>
@@ -29274,7 +29274,7 @@
         <v>230</v>
       </c>
       <c r="J25" t="n">
-        <v>230</v>
+        <v>218.3797849014816</v>
       </c>
       <c r="K25" t="n">
         <v>230</v>
@@ -29362,10 +29362,10 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
+        <v>183</v>
+      </c>
+      <c r="N26" t="n">
         <v>148.2898128463539</v>
-      </c>
-      <c r="N26" t="n">
-        <v>183</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -29432,10 +29432,10 @@
         <v>183</v>
       </c>
       <c r="J27" t="n">
-        <v>19.54682436935798</v>
+        <v>76.72764787669645</v>
       </c>
       <c r="K27" t="n">
-        <v>15.71323656002649</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -29444,7 +29444,7 @@
         <v>183</v>
       </c>
       <c r="N27" t="n">
-        <v>183</v>
+        <v>123.0961940438275</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -29511,7 +29511,7 @@
         <v>183</v>
       </c>
       <c r="J28" t="n">
-        <v>150.429346417681</v>
+        <v>183</v>
       </c>
       <c r="K28" t="n">
         <v>183</v>
@@ -29602,7 +29602,7 @@
         <v>201</v>
       </c>
       <c r="N29" t="n">
-        <v>130.2898128463535</v>
+        <v>130.2898128463537</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -29669,16 +29669,16 @@
         <v>201</v>
       </c>
       <c r="J30" t="n">
-        <v>34.29761661738385</v>
+        <v>57.14483712617317</v>
       </c>
       <c r="K30" t="n">
         <v>100.4129994297693</v>
       </c>
       <c r="L30" t="n">
-        <v>60.91744224318657</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>162.9297782656032</v>
+        <v>201</v>
       </c>
       <c r="N30" t="n">
         <v>123.0961940438275</v>
@@ -29906,28 +29906,28 @@
         <v>201</v>
       </c>
       <c r="J33" t="n">
-        <v>156.546824369358</v>
+        <v>19.54682436935798</v>
       </c>
       <c r="K33" t="n">
-        <v>13.63457742509133</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>60.10720623041205</v>
       </c>
       <c r="M33" t="n">
-        <v>162.9297782656032</v>
+        <v>201</v>
       </c>
       <c r="N33" t="n">
         <v>201</v>
       </c>
       <c r="O33" t="n">
-        <v>69.93676746419504</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>78.60608307552238</v>
+        <v>201</v>
       </c>
       <c r="R33" t="n">
         <v>201</v>
@@ -30073,10 +30073,10 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>145.9887040227496</v>
+        <v>201</v>
       </c>
       <c r="N35" t="n">
-        <v>185.3011088236041</v>
+        <v>130.2898128463537</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -30143,7 +30143,7 @@
         <v>201</v>
       </c>
       <c r="J36" t="n">
-        <v>132.1111800600533</v>
+        <v>79.65403059976975</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -30158,13 +30158,13 @@
         <v>201</v>
       </c>
       <c r="O36" t="n">
-        <v>69.93676746419504</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>78.60608307552238</v>
+        <v>201</v>
       </c>
       <c r="R36" t="n">
         <v>201</v>
@@ -30310,10 +30310,10 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>145.9887040227496</v>
+        <v>201</v>
       </c>
       <c r="N38" t="n">
-        <v>185.3011088236041</v>
+        <v>130.2898128463537</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -30380,7 +30380,7 @@
         <v>201</v>
       </c>
       <c r="J39" t="n">
-        <v>156.546824369358</v>
+        <v>79.65403059976975</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -30401,7 +30401,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>124.107206230412</v>
+        <v>201</v>
       </c>
       <c r="R39" t="n">
         <v>201</v>
@@ -30547,10 +30547,10 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
+        <v>148.2898128463537</v>
+      </c>
+      <c r="N41" t="n">
         <v>183</v>
-      </c>
-      <c r="N41" t="n">
-        <v>148.2898128463537</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -30617,13 +30617,13 @@
         <v>183</v>
       </c>
       <c r="J42" t="n">
-        <v>19.54682436935798</v>
+        <v>107.2511159590349</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>60.91744224318657</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>162.9297782656032</v>
@@ -30635,7 +30635,7 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>34.4930227225649</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>183</v>
@@ -30696,7 +30696,7 @@
         <v>183</v>
       </c>
       <c r="J43" t="n">
-        <v>183</v>
+        <v>164.5325981186378</v>
       </c>
       <c r="K43" t="n">
         <v>183</v>
@@ -30729,7 +30729,7 @@
         <v>183</v>
       </c>
       <c r="U43" t="n">
-        <v>150.9183584875727</v>
+        <v>183</v>
       </c>
       <c r="V43" t="n">
         <v>183</v>
@@ -30751,7 +30751,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.3266331658291458</v>
+        <v>1</v>
       </c>
       <c r="C44" t="n">
         <v>1</v>
@@ -30811,7 +30811,7 @@
         <v>1</v>
       </c>
       <c r="V44" t="n">
-        <v>1</v>
+        <v>0.3266331658291458</v>
       </c>
       <c r="W44" t="n">
         <v>1</v>
@@ -33248,10 +33248,10 @@
         <v>291.9478492462312</v>
       </c>
       <c r="O29" t="n">
-        <v>207.2478695740927</v>
+        <v>207.2478695740926</v>
       </c>
       <c r="P29" t="n">
-        <v>137.2870600406817</v>
+        <v>137.2870600406816</v>
       </c>
       <c r="Q29" t="n">
         <v>176.6891306532663</v>
@@ -34433,10 +34433,10 @@
         <v>291.9478492462312</v>
       </c>
       <c r="O44" t="n">
-        <v>207.2478695740926</v>
+        <v>207.2478695740925</v>
       </c>
       <c r="P44" t="n">
-        <v>137.2870600406816</v>
+        <v>137.2870600406815</v>
       </c>
       <c r="Q44" t="n">
         <v>176.6891306532663</v>
@@ -34822,25 +34822,25 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>207.9179175584304</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>114.8197919496652</v>
+        <v>36.58700057023064</v>
       </c>
       <c r="L3" t="n">
-        <v>76.08255775681344</v>
+        <v>121.854817399015</v>
       </c>
       <c r="M3" t="n">
         <v>235</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="O3" t="n">
+        <v>67.06323253580493</v>
+      </c>
+      <c r="P3" t="n">
         <v>235</v>
-      </c>
-      <c r="P3" t="n">
-        <v>61.6847832401415</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -35068,16 +35068,16 @@
         <v>76.08255775681344</v>
       </c>
       <c r="M6" t="n">
+        <v>139.917574619576</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
         <v>235</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>235</v>
-      </c>
-      <c r="O6" t="n">
-        <v>78.2327913794345</v>
-      </c>
-      <c r="P6" t="n">
-        <v>61.6847832401415</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -35299,22 +35299,22 @@
         <v>207.9179175584304</v>
       </c>
       <c r="K9" t="n">
-        <v>235</v>
+        <v>36.58700057023064</v>
       </c>
       <c r="L9" t="n">
         <v>76.08255775681344</v>
       </c>
       <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>139.917574619576</v>
+      </c>
+      <c r="O9" t="n">
         <v>235</v>
       </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>67.06323253580493</v>
-      </c>
       <c r="P9" t="n">
-        <v>109.4413426540017</v>
+        <v>235</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -35767,25 +35767,25 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>24.28706995197145</v>
       </c>
       <c r="J15" t="n">
-        <v>191.712637464336</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>36.58700057023064</v>
+        <v>121.88416221579</v>
       </c>
       <c r="L15" t="n">
-        <v>235</v>
+        <v>120.3802463909498</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>66.07022173439682</v>
       </c>
       <c r="N15" t="n">
         <v>105.9038059561725</v>
       </c>
       <c r="O15" t="n">
-        <v>104.3220622585407</v>
+        <v>235</v>
       </c>
       <c r="P15" t="n">
         <v>61.6847832401415</v>
@@ -36004,10 +36004,10 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>25.28706995197145</v>
+        <v>43.01465184450053</v>
       </c>
       <c r="J18" t="n">
-        <v>210.453175630642</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>36.58700057023064</v>
@@ -36016,19 +36016,19 @@
         <v>76.08255775681344</v>
       </c>
       <c r="M18" t="n">
-        <v>185.8054597358251</v>
+        <v>185.1589957115969</v>
       </c>
       <c r="N18" t="n">
         <v>106.9038059561725</v>
       </c>
       <c r="O18" t="n">
-        <v>67.06323253580493</v>
+        <v>235</v>
       </c>
       <c r="P18" t="n">
         <v>61.6847832401415</v>
       </c>
       <c r="Q18" t="n">
-        <v>151.3939169244776</v>
+        <v>168.669112268011</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -36083,7 +36083,7 @@
         <v>7.754218160676466</v>
       </c>
       <c r="I19" t="n">
-        <v>61.02178646279723</v>
+        <v>75.4379542159473</v>
       </c>
       <c r="J19" t="n">
         <v>235</v>
@@ -36241,28 +36241,28 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>25.28706995197146</v>
+        <v>25.28706995197145</v>
       </c>
       <c r="J21" t="n">
-        <v>210.453175630642</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>36.58700057023064</v>
       </c>
       <c r="L21" t="n">
-        <v>142.2065703458604</v>
+        <v>76.08255775681344</v>
       </c>
       <c r="M21" t="n">
         <v>67.07022173439682</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>106.9038059561725</v>
       </c>
       <c r="O21" t="n">
         <v>235</v>
       </c>
       <c r="P21" t="n">
-        <v>61.6847832401415</v>
+        <v>226.9689854127091</v>
       </c>
       <c r="Q21" t="n">
         <v>151.3939169244776</v>
@@ -36317,13 +36317,13 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>7.754218160676466</v>
       </c>
       <c r="I22" t="n">
-        <v>75.43795421594731</v>
+        <v>75.4379542159473</v>
       </c>
       <c r="J22" t="n">
-        <v>213.4596499718953</v>
+        <v>213.4596499718946</v>
       </c>
       <c r="K22" t="n">
         <v>26.74906226443071</v>
@@ -36353,10 +36353,10 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>23.11133513308656</v>
+        <v>23.11133513308655</v>
       </c>
       <c r="U22" t="n">
-        <v>79.0816415124273</v>
+        <v>79.08164151242731</v>
       </c>
       <c r="V22" t="n">
         <v>30.82968978378381</v>
@@ -36478,28 +36478,28 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>25.28706995197146</v>
+        <v>25.28706995197145</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>210.453175630642</v>
       </c>
       <c r="K24" t="n">
-        <v>235</v>
+        <v>36.58700057023064</v>
       </c>
       <c r="L24" t="n">
-        <v>235</v>
+        <v>76.08255775681344</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>67.07022173439682</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>160.875432260563</v>
       </c>
       <c r="O24" t="n">
-        <v>207.9101448380715</v>
+        <v>67.06323253580493</v>
       </c>
       <c r="P24" t="n">
-        <v>61.6847832401415</v>
+        <v>118.2882999825664</v>
       </c>
       <c r="Q24" t="n">
         <v>151.3939169244776</v>
@@ -36554,13 +36554,13 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>7.754218160676459</v>
+        <v>7.754218160676466</v>
       </c>
       <c r="I25" t="n">
-        <v>75.43795421594731</v>
+        <v>75.4379542159473</v>
       </c>
       <c r="J25" t="n">
-        <v>229.3908198939536</v>
+        <v>235</v>
       </c>
       <c r="K25" t="n">
         <v>26.74906226443071</v>
@@ -36590,10 +36590,10 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>23.11133513308656</v>
+        <v>23.11133513308655</v>
       </c>
       <c r="U25" t="n">
-        <v>79.0816415124273</v>
+        <v>79.08164151242731</v>
       </c>
       <c r="V25" t="n">
         <v>30.82968978378381</v>
@@ -36718,10 +36718,10 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>57.18082350733847</v>
       </c>
       <c r="K27" t="n">
-        <v>52.30023713025713</v>
+        <v>36.58700057023064</v>
       </c>
       <c r="L27" t="n">
         <v>76.08255775681344</v>
@@ -36730,7 +36730,7 @@
         <v>20.07022173439682</v>
       </c>
       <c r="N27" t="n">
-        <v>59.9038059561725</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>67.06323253580493</v>
@@ -36797,7 +36797,7 @@
         <v>6.091649674775283</v>
       </c>
       <c r="J28" t="n">
-        <v>32.84924521697209</v>
+        <v>65.41989879929108</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -36891,10 +36891,10 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>137.0000000000003</v>
+        <v>137.0000000000002</v>
       </c>
       <c r="P29" t="n">
-        <v>137.0000000000003</v>
+        <v>137.0000000000002</v>
       </c>
       <c r="Q29" t="n">
         <v>3.866446325780913</v>
@@ -36955,16 +36955,16 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>14.75079224802587</v>
+        <v>37.59801275681519</v>
       </c>
       <c r="K30" t="n">
         <v>137</v>
       </c>
       <c r="L30" t="n">
-        <v>137</v>
+        <v>76.08255775681344</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>38.07022173439682</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -37034,7 +37034,7 @@
         <v>46.4379542159473</v>
       </c>
       <c r="J31" t="n">
-        <v>121.0806178599954</v>
+        <v>121.080617859995</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -37192,28 +37192,28 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>50.22157799532198</v>
+        <v>36.58700057023064</v>
       </c>
       <c r="L33" t="n">
-        <v>76.08255775681344</v>
+        <v>136.1897639872255</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>38.07022173439682</v>
       </c>
       <c r="N33" t="n">
         <v>77.9038059561725</v>
       </c>
       <c r="O33" t="n">
-        <v>137</v>
+        <v>67.06323253580493</v>
       </c>
       <c r="P33" t="n">
         <v>61.6847832401415</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>122.3939169244776</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37271,7 +37271,7 @@
         <v>46.43795421594731</v>
       </c>
       <c r="J34" t="n">
-        <v>121.0806178599965</v>
+        <v>121.0806178599962</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -37429,7 +37429,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>112.5643556906953</v>
+        <v>60.10720623041176</v>
       </c>
       <c r="K36" t="n">
         <v>36.58700057023064</v>
@@ -37444,13 +37444,13 @@
         <v>77.9038059561725</v>
       </c>
       <c r="O36" t="n">
-        <v>137</v>
+        <v>67.06323253580493</v>
       </c>
       <c r="P36" t="n">
         <v>61.6847832401415</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>122.3939169244776</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37505,10 +37505,10 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>46.43795421594731</v>
+        <v>30.51857207594391</v>
       </c>
       <c r="J37" t="n">
-        <v>121.0806178599973</v>
+        <v>137</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -37666,7 +37666,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>137</v>
+        <v>60.10720623041176</v>
       </c>
       <c r="K39" t="n">
         <v>36.58700057023064</v>
@@ -37687,7 +37687,7 @@
         <v>61.6847832401415</v>
       </c>
       <c r="Q39" t="n">
-        <v>45.5011231548896</v>
+        <v>122.3939169244776</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37742,10 +37742,10 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>46.4379542159473</v>
+        <v>46.43795421594731</v>
       </c>
       <c r="J40" t="n">
-        <v>121.0806178599957</v>
+        <v>121.0806178599966</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -37778,7 +37778,7 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>50.08164151242731</v>
+        <v>50.0816415124273</v>
       </c>
       <c r="V40" t="n">
         <v>1.829689783783806</v>
@@ -37903,13 +37903,13 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>87.70429158967694</v>
       </c>
       <c r="K42" t="n">
         <v>36.58700057023064</v>
       </c>
       <c r="L42" t="n">
-        <v>137</v>
+        <v>76.08255775681344</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -37921,7 +37921,7 @@
         <v>67.06323253580493</v>
       </c>
       <c r="P42" t="n">
-        <v>96.1778059627064</v>
+        <v>61.6847832401415</v>
       </c>
       <c r="Q42" t="n">
         <v>104.3939169244776</v>
@@ -37982,7 +37982,7 @@
         <v>6.091649674775276</v>
       </c>
       <c r="J43" t="n">
-        <v>65.41989879929108</v>
+        <v>46.95249691792887</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -38015,7 +38015,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>32.08164151242731</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -38076,10 +38076,10 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>137.0000000000002</v>
+        <v>137.0000000000001</v>
       </c>
       <c r="P44" t="n">
-        <v>137.0000000000002</v>
+        <v>137.0000000000001</v>
       </c>
       <c r="Q44" t="n">
         <v>3.866446325780913</v>
